--- a/IEF_Home/UploadedFiles/4_PY_CIRCOMOD_D4.1_v1.0.xlsx
+++ b/IEF_Home/UploadedFiles/4_PY_CIRCOMOD_D4.1_v1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan Pauliuk\Dropbox\Data_Compilation_CIRCOMOD_2023\CIRCOMOD_InputDatabase_D2.2\Pre_Validation\CE_Potentials_Technologies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan Pauliuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FB0532-334E-4789-AE0F-E99B663CDD5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DB6DF5-EA46-4B10-B9FD-47B9CEAC2817}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="4524" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15678" windowHeight="5850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="372">
   <si>
     <t>Dataset information</t>
   </si>
@@ -411,12 +411,6 @@
     <t>[a] Copper cathode production, Hydrometallurgy (leaching, SX, EW)</t>
   </si>
   <si>
-    <t>Oxide ore</t>
-  </si>
-  <si>
-    <t>Copper, cathode</t>
-  </si>
-  <si>
     <t>[PU] Hydro_Copper</t>
   </si>
   <si>
@@ -429,15 +423,9 @@
     <t>[a] Copper anode production (Flash smelting and converting)</t>
   </si>
   <si>
-    <t>Copper concentrate, sulfide ore</t>
-  </si>
-  <si>
     <t>from technosphere (material)</t>
   </si>
   <si>
-    <t>Copper, anode</t>
-  </si>
-  <si>
     <t>[PU] Pyro_Flash_Copper</t>
   </si>
   <si>
@@ -468,9 +456,6 @@
     <t>[a] Secondary copper production, from low grade scrap</t>
   </si>
   <si>
-    <t>Copper scrap, low grade</t>
-  </si>
-  <si>
     <t>[PU] Sec_Copper_Low_Grade</t>
   </si>
   <si>
@@ -480,9 +465,6 @@
     <t>[a] Secondary copper production, from medium grade scrap</t>
   </si>
   <si>
-    <t>Copper scrap, medium grade</t>
-  </si>
-  <si>
     <t>[PU] Sec_Copper_Med_Grade</t>
   </si>
   <si>
@@ -492,9 +474,6 @@
     <t>[a] Secondary copper production, from high grade scrap</t>
   </si>
   <si>
-    <t>Copper scrap, high grade</t>
-  </si>
-  <si>
     <t>[PU] Sec_Copper_High_Grade</t>
   </si>
   <si>
@@ -504,12 +483,6 @@
     <t>[Zhang] Copper concentrate production, slag recycling</t>
   </si>
   <si>
-    <t>Smelting slag</t>
-  </si>
-  <si>
-    <t>Copper concentrate, from slag</t>
-  </si>
-  <si>
     <t>[PU] Conc_from_Slag</t>
   </si>
   <si>
@@ -519,12 +492,6 @@
     <t xml:space="preserve">[Zhang] Secondary copper production, ash recycling </t>
   </si>
   <si>
-    <t>Copper ash</t>
-  </si>
-  <si>
-    <t>Recycling of 1kg of copper ash</t>
-  </si>
-  <si>
     <t>[PU] Copper_from_ash</t>
   </si>
   <si>
@@ -534,12 +501,6 @@
     <t>[Zhang2021] Processing of anode slime, from copper waste</t>
   </si>
   <si>
-    <t>Anode slime</t>
-  </si>
-  <si>
-    <t>Extraction of metals from anode slime 1kg</t>
-  </si>
-  <si>
     <t>[PU] AS_treatment_from_Copper_Waste</t>
   </si>
   <si>
@@ -558,9 +519,6 @@
     <t>[a] Beneficiation, sulfide ore (Crushing, grinding, flotation)</t>
   </si>
   <si>
-    <t>Sulphide ore</t>
-  </si>
-  <si>
     <t>[PU] Sulf_Ore_Conc</t>
   </si>
   <si>
@@ -577,9 +535,6 @@
   </si>
   <si>
     <t>[Becci] Secondary copper production via biometallurgy, from low grade scrap</t>
-  </si>
-  <si>
-    <t>Low grade scrap from shredded PCBs</t>
   </si>
   <si>
     <t>from technosphere (other)</t>
@@ -1150,6 +1105,54 @@
   </si>
   <si>
     <t>Result of academic MFA work</t>
+  </si>
+  <si>
+    <t>oxide ore</t>
+  </si>
+  <si>
+    <t>copper concentrate, sulfide ore</t>
+  </si>
+  <si>
+    <t>copper, anode</t>
+  </si>
+  <si>
+    <t>copper scrap, low grade</t>
+  </si>
+  <si>
+    <t>copper scrap, medium grade</t>
+  </si>
+  <si>
+    <t>copper scrap, high grade</t>
+  </si>
+  <si>
+    <t>smelting slag</t>
+  </si>
+  <si>
+    <t>copper ash</t>
+  </si>
+  <si>
+    <t>anode slime</t>
+  </si>
+  <si>
+    <t>sulphide ore</t>
+  </si>
+  <si>
+    <t>low grade scrap from shredded PCBs</t>
+  </si>
+  <si>
+    <t>copper cathode</t>
+  </si>
+  <si>
+    <t>copper anode</t>
+  </si>
+  <si>
+    <t>copper concentrate, from slag</t>
+  </si>
+  <si>
+    <t>extraction of metals from anode slime 1kg</t>
+  </si>
+  <si>
+    <t>recycling of 1kg of copper ash</t>
   </si>
 </sst>
 </file>
@@ -1661,22 +1664,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1688,6 +1679,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2053,13 +2056,13 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="76" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="77"/>
       <c r="D2" s="77"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="76" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="77"/>
@@ -2082,7 +2085,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="78" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -2111,7 +2114,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>7</v>
@@ -2129,7 +2132,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>7</v>
@@ -2148,7 +2151,7 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="79" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="41" t="s">
@@ -2203,7 +2206,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>7</v>
@@ -2227,7 +2230,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>7</v>
@@ -2250,7 +2253,7 @@
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="80" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="28" t="s">
@@ -2487,7 +2490,7 @@
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="81" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="28" t="s">
@@ -2530,7 +2533,7 @@
         <v>64</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
@@ -2577,7 +2580,7 @@
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="82" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="36" t="s">
@@ -3021,7 +3024,7 @@
         <v>93</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>7</v>
@@ -3037,7 +3040,7 @@
         <v>94</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>7</v>
@@ -3048,14 +3051,14 @@
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="83" t="s">
         <v>95</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>96</v>
       </c>
       <c r="D53" s="71" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>7</v>
@@ -3070,7 +3073,7 @@
         <v>97</v>
       </c>
       <c r="D54" s="71" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>7</v>
@@ -3085,7 +3088,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>7</v>
@@ -3100,7 +3103,7 @@
         <v>99</v>
       </c>
       <c r="D56" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>7</v>
@@ -3115,7 +3118,7 @@
         <v>100</v>
       </c>
       <c r="D57" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>7</v>
@@ -3130,7 +3133,7 @@
         <v>101</v>
       </c>
       <c r="D58" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>7</v>
@@ -3145,7 +3148,7 @@
         <v>102</v>
       </c>
       <c r="D59" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>7</v>
@@ -3170,14 +3173,14 @@
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" s="79" t="s">
+      <c r="B61" s="84" t="s">
         <v>104</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>105</v>
       </c>
       <c r="D61" s="71" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>7</v>
@@ -3271,7 +3274,7 @@
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" s="80" t="s">
+      <c r="B68" s="85" t="s">
         <v>114</v>
       </c>
       <c r="C68" s="43" t="s">
@@ -3336,16 +3339,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B26:B52"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="B61:B67"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B20"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B26:B52"/>
-    <mergeCell ref="B53:B60"/>
-    <mergeCell ref="B61:B67"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3403,7 +3406,7 @@
         <v>42</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="K1" s="50" t="s">
         <v>50</v>
@@ -3418,22 +3421,22 @@
     </row>
     <row r="2" spans="1:15" s="74" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="59" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="B2" s="73" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>122</v>
       </c>
       <c r="D2" s="73" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="E2" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F2" s="74" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G2" s="58">
         <v>1</v>
@@ -3457,19 +3460,19 @@
         <v>126</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>127</v>
+        <v>356</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>122</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G3" s="58">
         <v>0.7</v>
@@ -3484,34 +3487,34 @@
         <v>37</v>
       </c>
       <c r="K3" s="58" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L3" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="58" t="s">
         <v>129</v>
-      </c>
-      <c r="M3" s="58" t="s">
-        <v>131</v>
       </c>
       <c r="O3" s="75"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G4" s="58">
         <v>28</v>
@@ -3526,33 +3529,33 @@
         <v>37</v>
       </c>
       <c r="K4" s="58" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L4" s="67" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M4" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="62" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F5" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G5" s="58">
         <v>28</v>
@@ -3567,33 +3570,33 @@
         <v>37</v>
       </c>
       <c r="K5" s="58" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L5" s="67" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M5" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="62" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G6" s="58">
         <v>28</v>
@@ -3608,33 +3611,33 @@
         <v>37</v>
       </c>
       <c r="K6" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="L6" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="L6" s="67" t="s">
-        <v>141</v>
-      </c>
       <c r="M6" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="62" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>135</v>
+        <v>358</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F7" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G7" s="58">
         <v>99.25</v>
@@ -3649,33 +3652,33 @@
         <v>37</v>
       </c>
       <c r="K7" s="58" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L7" s="67" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M7" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="62" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>146</v>
+        <v>359</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G8" s="58">
         <v>30</v>
@@ -3690,33 +3693,33 @@
         <v>37</v>
       </c>
       <c r="K8" s="58" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L8" s="67" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="62" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>150</v>
+        <v>360</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F9" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G9" s="58">
         <v>50</v>
@@ -3731,33 +3734,33 @@
         <v>37</v>
       </c>
       <c r="K9" s="58" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="L9" s="67" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="62" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>154</v>
+        <v>361</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D10" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G10" s="58">
         <v>95</v>
@@ -3772,33 +3775,33 @@
         <v>37</v>
       </c>
       <c r="K10" s="58" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="L10" s="67" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="62" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>158</v>
+        <v>362</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>159</v>
+        <v>369</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F11" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G11" s="58">
         <v>9</v>
@@ -3813,33 +3816,33 @@
         <v>37</v>
       </c>
       <c r="K11" s="58" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="L11" s="67" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="62" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>164</v>
+        <v>371</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G12" s="58">
         <v>1</v>
@@ -3854,33 +3857,33 @@
         <v>37</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L12" s="67" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="62" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>169</v>
+        <v>370</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G13" s="58">
         <v>1</v>
@@ -3895,33 +3898,33 @@
         <v>37</v>
       </c>
       <c r="K13" s="58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L13" s="67" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="M13" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="62" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>169</v>
+        <v>370</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G14" s="58">
         <v>1</v>
@@ -3936,33 +3939,33 @@
         <v>37</v>
       </c>
       <c r="K14" s="58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L14" s="67" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="M14" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="62" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>169</v>
+        <v>370</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G15" s="58">
         <v>1</v>
@@ -3977,33 +3980,33 @@
         <v>37</v>
       </c>
       <c r="K15" s="58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L15" s="67" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="M15" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="62" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>176</v>
+        <v>365</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>122</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F16" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G16" s="58">
         <v>25</v>
@@ -4018,33 +4021,33 @@
         <v>37</v>
       </c>
       <c r="K16" s="58" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="L16" s="67" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="M16" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="62" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>135</v>
+        <v>368</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G17" s="68">
         <v>28</v>
@@ -4059,33 +4062,33 @@
         <v>37</v>
       </c>
       <c r="K17" s="58" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="L17" s="67" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="M17" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="62" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F18" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G18" s="68">
         <v>24</v>
@@ -4100,33 +4103,33 @@
         <v>37</v>
       </c>
       <c r="K18" s="58" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L18" s="67" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="M18" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="62" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G19" s="68">
         <v>23</v>
@@ -4141,33 +4144,33 @@
         <v>37</v>
       </c>
       <c r="K19" s="58" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L19" s="67" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="M19" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="62" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F20" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G20" s="68">
         <v>14</v>
@@ -4182,33 +4185,33 @@
         <v>37</v>
       </c>
       <c r="K20" s="58" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L20" s="67" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M20" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="65" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F21" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G21" s="68">
         <v>95</v>
@@ -4223,35 +4226,35 @@
         <v>37</v>
       </c>
       <c r="K21" s="58" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="L21" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M21" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N21" s="58"/>
       <c r="O21" s="58"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F22" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G22" s="68">
         <v>95</v>
@@ -4266,35 +4269,35 @@
         <v>37</v>
       </c>
       <c r="K22" s="58" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="L22" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M22" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N22" s="58"/>
       <c r="O22" s="58"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D23" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E23" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F23" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G23" s="68">
         <v>95</v>
@@ -4309,35 +4312,35 @@
         <v>37</v>
       </c>
       <c r="K23" s="58" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="L23" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M23" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N23" s="58"/>
       <c r="O23" s="58"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="65" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D24" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F24" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G24" s="68">
         <v>95</v>
@@ -4352,35 +4355,35 @@
         <v>37</v>
       </c>
       <c r="K24" s="58" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="L24" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M24" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N24" s="58"/>
       <c r="O24" s="58"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="65" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F25" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G25" s="68">
         <v>95</v>
@@ -4395,35 +4398,35 @@
         <v>37</v>
       </c>
       <c r="K25" s="58" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L25" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M25" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N25" s="58"/>
       <c r="O25" s="58"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="65" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D26" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F26" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G26" s="68">
         <v>95</v>
@@ -4439,32 +4442,32 @@
       </c>
       <c r="K26" s="58"/>
       <c r="L26" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M26" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N26" s="58"/>
       <c r="O26" s="58"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="65" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B27" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D27" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E27" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F27" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G27" s="68">
         <v>95</v>
@@ -4479,35 +4482,35 @@
         <v>37</v>
       </c>
       <c r="K27" s="58" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L27" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M27" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N27" s="58"/>
       <c r="O27" s="58"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="65" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G28" s="68">
         <v>95</v>
@@ -4522,35 +4525,35 @@
         <v>37</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L28" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M28" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N28" s="58"/>
       <c r="O28" s="58"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="65" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" t="s">
+        <v>343</v>
+      </c>
+      <c r="F29" t="s">
         <v>342</v>
-      </c>
-      <c r="B29" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>359</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" t="s">
-        <v>358</v>
-      </c>
-      <c r="F29" t="s">
-        <v>357</v>
       </c>
       <c r="G29" s="68">
         <v>95</v>
@@ -4565,35 +4568,35 @@
         <v>37</v>
       </c>
       <c r="K29" s="58" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L29" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M29" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N29" s="58"/>
       <c r="O29" s="58"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="B30" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" t="s">
         <v>343</v>
       </c>
-      <c r="B30" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>359</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="E30" t="s">
-        <v>358</v>
-      </c>
       <c r="F30" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G30" s="68">
         <v>95</v>
@@ -4608,35 +4611,35 @@
         <v>37</v>
       </c>
       <c r="K30" s="58" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="L30" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M30" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N30" s="58"/>
       <c r="O30" s="58"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="65" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="58" t="s">
         <v>344</v>
       </c>
-      <c r="B31" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>359</v>
-      </c>
       <c r="D31" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E31" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F31" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G31" s="68">
         <v>95</v>
@@ -4651,35 +4654,35 @@
         <v>37</v>
       </c>
       <c r="K31" s="58" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L31" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M31" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N31" s="58"/>
       <c r="O31" s="58"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="65" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E32" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F32" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G32" s="68">
         <v>95</v>
@@ -4695,32 +4698,32 @@
       </c>
       <c r="K32" s="58"/>
       <c r="L32" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M32" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N32" s="58"/>
       <c r="O32" s="58"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="65" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="B33" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E33" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F33" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G33" s="68">
         <v>95</v>
@@ -4736,32 +4739,32 @@
       </c>
       <c r="K33" s="58"/>
       <c r="L33" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M33" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N33" s="58"/>
       <c r="O33" s="58"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="65" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D34" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E34" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F34" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G34" s="68">
         <v>95</v>
@@ -4777,32 +4780,32 @@
       </c>
       <c r="K34" s="58"/>
       <c r="L34" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M34" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N34" s="58"/>
       <c r="O34" s="58"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="65" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B35" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D35" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E35" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F35" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G35" s="68">
         <v>95</v>
@@ -4817,35 +4820,35 @@
         <v>37</v>
       </c>
       <c r="K35" s="58" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L35" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M35" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N35" s="58"/>
       <c r="O35" s="58"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="65" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D36" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E36" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F36" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G36" s="68">
         <v>95</v>
@@ -4860,35 +4863,35 @@
         <v>37</v>
       </c>
       <c r="K36" s="58" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L36" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M36" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N36" s="58"/>
       <c r="O36" s="58"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="65" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="B37" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D37" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E37" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F37" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G37" s="68">
         <v>95</v>
@@ -4903,35 +4906,35 @@
         <v>37</v>
       </c>
       <c r="K37" s="58" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="L37" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M37" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N37" s="58"/>
       <c r="O37" s="58"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="65" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D38" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F38" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G38" s="68">
         <v>95</v>
@@ -4946,35 +4949,35 @@
         <v>37</v>
       </c>
       <c r="K38" s="58" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L38" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M38" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N38" s="58"/>
       <c r="O38" s="58"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="65" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B39" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D39" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F39" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G39" s="68">
         <v>95</v>
@@ -4990,32 +4993,32 @@
       </c>
       <c r="K39" s="58"/>
       <c r="L39" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M39" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N39" s="58"/>
       <c r="O39" s="58"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="65" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D40" s="58" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F40" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G40" s="68">
         <v>95</v>
@@ -5031,32 +5034,32 @@
       </c>
       <c r="K40" s="58"/>
       <c r="L40" s="58" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M40" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N40" s="58"/>
       <c r="O40" s="58"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="67" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
       <c r="C41" s="58" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D41" s="58" t="s">
-        <v>169</v>
+        <v>370</v>
       </c>
       <c r="E41" s="58" t="s">
         <v>123</v>
       </c>
       <c r="F41" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G41" s="68">
         <v>1</v>
@@ -5071,13 +5074,13 @@
         <v>37</v>
       </c>
       <c r="K41" s="58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L41" s="67" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M41" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -5106,45 +5109,45 @@
   <sheetData>
     <row r="2" spans="1:7" ht="55.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="54" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F2" s="56" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B3" s="62" t="s">
         <v>126</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D3" s="63">
         <v>45212</v>
       </c>
       <c r="E3" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F3" s="58" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G3" s="58">
         <v>2</v>
@@ -5157,7 +5160,7 @@
       <c r="D4" s="58"/>
       <c r="E4" s="58"/>
       <c r="F4" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G4" s="58"/>
     </row>
@@ -5168,7 +5171,7 @@
       <c r="D5" s="58"/>
       <c r="E5" s="58"/>
       <c r="F5" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G5" s="58"/>
     </row>
@@ -5179,7 +5182,7 @@
       <c r="D6" s="58"/>
       <c r="E6" s="58"/>
       <c r="F6" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G6" s="58"/>
     </row>
@@ -5190,7 +5193,7 @@
       <c r="D7" s="58"/>
       <c r="E7" s="58"/>
       <c r="F7" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G7" s="58"/>
     </row>
@@ -5205,25 +5208,25 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="67" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D9" s="63">
         <v>45212</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5233,7 +5236,7 @@
       <c r="D10" s="58"/>
       <c r="E10" s="58"/>
       <c r="F10" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G10" s="58"/>
     </row>
@@ -5244,7 +5247,7 @@
       <c r="D11" s="58"/>
       <c r="E11" s="58"/>
       <c r="F11" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G11" s="58"/>
     </row>
@@ -5255,7 +5258,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="F12" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G12" s="58"/>
     </row>
@@ -5266,7 +5269,7 @@
       <c r="D13" s="58"/>
       <c r="E13" s="58"/>
       <c r="F13" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G13" s="58"/>
     </row>
@@ -5281,25 +5284,25 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="67" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B15" s="62" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D15" s="63">
         <v>45212</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5309,7 +5312,7 @@
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
       <c r="F16" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G16" s="58"/>
     </row>
@@ -5320,7 +5323,7 @@
       <c r="D17" s="58"/>
       <c r="E17" s="58"/>
       <c r="F17" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G17" s="58"/>
     </row>
@@ -5331,7 +5334,7 @@
       <c r="D18" s="58"/>
       <c r="E18" s="58"/>
       <c r="F18" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G18" s="58"/>
     </row>
@@ -5342,7 +5345,7 @@
       <c r="D19" s="58"/>
       <c r="E19" s="58"/>
       <c r="F19" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G19" s="58"/>
     </row>
@@ -5357,25 +5360,25 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="67" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B21" s="62" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D21" s="63">
         <v>45212</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F21" s="58" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G21" s="58" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5385,7 +5388,7 @@
       <c r="D22" s="58"/>
       <c r="E22" s="58"/>
       <c r="F22" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G22" s="58"/>
     </row>
@@ -5396,7 +5399,7 @@
       <c r="D23" s="58"/>
       <c r="E23" s="58"/>
       <c r="F23" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G23" s="58"/>
     </row>
@@ -5407,7 +5410,7 @@
       <c r="D24" s="58"/>
       <c r="E24" s="58"/>
       <c r="F24" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G24" s="58"/>
     </row>
@@ -5418,7 +5421,7 @@
       <c r="D25" s="58"/>
       <c r="E25" s="58"/>
       <c r="F25" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G25" s="58"/>
     </row>
@@ -5435,22 +5438,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="67" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B27" s="62" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D27" s="63">
         <v>45212</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F27" s="58" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G27" s="58"/>
     </row>
@@ -5461,7 +5464,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="58"/>
       <c r="F28" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G28" s="58"/>
     </row>
@@ -5472,7 +5475,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="58"/>
       <c r="F29" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G29" s="58"/>
     </row>
@@ -5483,7 +5486,7 @@
       <c r="D30" s="58"/>
       <c r="E30" s="58"/>
       <c r="F30" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G30" s="58"/>
     </row>
@@ -5494,7 +5497,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="58"/>
       <c r="F31" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G31" s="58"/>
     </row>
@@ -5509,25 +5512,25 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="67" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B33" s="62" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D33" s="63">
         <v>45212</v>
       </c>
       <c r="E33" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="G33" s="58" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5537,7 +5540,7 @@
       <c r="D34" s="58"/>
       <c r="E34" s="58"/>
       <c r="F34" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G34" s="58"/>
     </row>
@@ -5548,7 +5551,7 @@
       <c r="D35" s="58"/>
       <c r="E35" s="58"/>
       <c r="F35" s="58" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="G35" s="58"/>
     </row>
@@ -5559,7 +5562,7 @@
       <c r="D36" s="58"/>
       <c r="E36" s="58"/>
       <c r="F36" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G36" s="58"/>
     </row>
@@ -5570,7 +5573,7 @@
       <c r="D37" s="58"/>
       <c r="E37" s="58"/>
       <c r="F37" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G37" s="58"/>
     </row>
@@ -5585,25 +5588,25 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="67" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D39" s="63">
         <v>45212</v>
       </c>
       <c r="E39" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F39" s="58" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G39" s="58" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5613,7 +5616,7 @@
       <c r="D40" s="58"/>
       <c r="E40" s="58"/>
       <c r="F40" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G40" s="58"/>
     </row>
@@ -5624,7 +5627,7 @@
       <c r="D41" s="58"/>
       <c r="E41" s="58"/>
       <c r="F41" s="58" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G41" s="58"/>
     </row>
@@ -5635,7 +5638,7 @@
       <c r="D42" s="58"/>
       <c r="E42" s="58"/>
       <c r="F42" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G42" s="58"/>
     </row>
@@ -5646,7 +5649,7 @@
       <c r="D43" s="58"/>
       <c r="E43" s="58"/>
       <c r="F43" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G43" s="58"/>
     </row>
@@ -5661,25 +5664,25 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="67" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C45" s="58" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D45" s="63">
         <v>45212</v>
       </c>
       <c r="E45" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G45" s="58" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5689,7 +5692,7 @@
       <c r="D46" s="58"/>
       <c r="E46" s="58"/>
       <c r="F46" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G46" s="58"/>
     </row>
@@ -5700,7 +5703,7 @@
       <c r="D47" s="58"/>
       <c r="E47" s="58"/>
       <c r="F47" s="58" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G47" s="58"/>
     </row>
@@ -5711,7 +5714,7 @@
       <c r="D48" s="58"/>
       <c r="E48" s="58"/>
       <c r="F48" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G48" s="58"/>
     </row>
@@ -5722,7 +5725,7 @@
       <c r="D49" s="58"/>
       <c r="E49" s="58"/>
       <c r="F49" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G49" s="58"/>
     </row>
@@ -5737,22 +5740,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="67" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B51" s="62" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C51" s="58" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D51" s="63">
         <v>45212</v>
       </c>
       <c r="E51" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F51" s="58" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="G51" s="58">
         <v>8</v>
@@ -5765,7 +5768,7 @@
       <c r="D52" s="58"/>
       <c r="E52" s="58"/>
       <c r="F52" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G52" s="58"/>
     </row>
@@ -5776,7 +5779,7 @@
       <c r="D53" s="58"/>
       <c r="E53" s="58"/>
       <c r="F53" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G53" s="58"/>
     </row>
@@ -5787,7 +5790,7 @@
       <c r="D54" s="58"/>
       <c r="E54" s="58"/>
       <c r="F54" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G54" s="58"/>
     </row>
@@ -5798,7 +5801,7 @@
       <c r="D55" s="58"/>
       <c r="E55" s="58"/>
       <c r="F55" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G55" s="58"/>
     </row>
@@ -5813,22 +5816,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="67" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B57" s="62" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C57" s="58" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D57" s="63">
         <v>45212</v>
       </c>
       <c r="E57" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F57" s="58" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="G57" s="58">
         <v>8</v>
@@ -5841,7 +5844,7 @@
       <c r="D58" s="58"/>
       <c r="E58" s="58"/>
       <c r="F58" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G58" s="58"/>
     </row>
@@ -5852,7 +5855,7 @@
       <c r="D59" s="58"/>
       <c r="E59" s="58"/>
       <c r="F59" s="58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G59" s="58"/>
     </row>
@@ -5863,7 +5866,7 @@
       <c r="D60" s="58"/>
       <c r="E60" s="58"/>
       <c r="F60" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G60" s="58"/>
     </row>
@@ -5874,7 +5877,7 @@
       <c r="D61" s="58"/>
       <c r="E61" s="58"/>
       <c r="F61" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G61" s="58"/>
     </row>
@@ -5889,20 +5892,20 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="67" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C63" s="58"/>
       <c r="D63" s="63">
         <v>45212</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F63" s="58" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G63" s="58">
         <v>9</v>
@@ -5915,7 +5918,7 @@
       <c r="D64" s="58"/>
       <c r="E64" s="58"/>
       <c r="F64" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G64" s="58"/>
     </row>
@@ -5926,7 +5929,7 @@
       <c r="D65" s="58"/>
       <c r="E65" s="58"/>
       <c r="F65" s="58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G65" s="58"/>
     </row>
@@ -5937,7 +5940,7 @@
       <c r="D66" s="58"/>
       <c r="E66" s="58"/>
       <c r="F66" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G66" s="58"/>
     </row>
@@ -5948,7 +5951,7 @@
       <c r="D67" s="58"/>
       <c r="E67" s="58"/>
       <c r="F67" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G67" s="58"/>
     </row>
@@ -5963,20 +5966,20 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="67" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B69" s="62" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C69" s="58"/>
       <c r="D69" s="63">
         <v>45212</v>
       </c>
       <c r="E69" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F69" s="58" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="G69" s="58">
         <v>3</v>
@@ -5989,7 +5992,7 @@
       <c r="D70" s="58"/>
       <c r="E70" s="58"/>
       <c r="F70" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G70" s="58"/>
     </row>
@@ -6000,7 +6003,7 @@
       <c r="D71" s="58"/>
       <c r="E71" s="58"/>
       <c r="F71" s="58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G71" s="58"/>
     </row>
@@ -6011,7 +6014,7 @@
       <c r="D72" s="58"/>
       <c r="E72" s="58"/>
       <c r="F72" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G72" s="58"/>
     </row>
@@ -6022,7 +6025,7 @@
       <c r="D73" s="58"/>
       <c r="E73" s="58"/>
       <c r="F73" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G73" s="58"/>
     </row>
@@ -6037,20 +6040,20 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="67" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B75" s="62" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C75" s="58"/>
       <c r="D75" s="63">
         <v>45212</v>
       </c>
       <c r="E75" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F75" s="58" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="G75" s="58">
         <v>8</v>
@@ -6063,7 +6066,7 @@
       <c r="D76" s="58"/>
       <c r="E76" s="58"/>
       <c r="F76" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G76" s="58"/>
     </row>
@@ -6074,7 +6077,7 @@
       <c r="D77" s="58"/>
       <c r="E77" s="58"/>
       <c r="F77" s="58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G77" s="58"/>
     </row>
@@ -6085,7 +6088,7 @@
       <c r="D78" s="58"/>
       <c r="E78" s="58"/>
       <c r="F78" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G78" s="58"/>
     </row>
@@ -6096,7 +6099,7 @@
       <c r="D79" s="58"/>
       <c r="E79" s="58"/>
       <c r="F79" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G79" s="58"/>
     </row>
@@ -6111,25 +6114,25 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="67" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B81" s="62" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C81" s="58" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D81" s="63">
         <v>45212</v>
       </c>
       <c r="E81" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F81" s="58" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="G81" s="58" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6139,7 +6142,7 @@
       <c r="D82" s="58"/>
       <c r="E82" s="58"/>
       <c r="F82" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G82" s="58"/>
     </row>
@@ -6150,7 +6153,7 @@
       <c r="D83" s="58"/>
       <c r="E83" s="58"/>
       <c r="F83" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G83" s="58"/>
     </row>
@@ -6161,7 +6164,7 @@
       <c r="D84" s="58"/>
       <c r="E84" s="58"/>
       <c r="F84" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G84" s="58"/>
     </row>
@@ -6172,7 +6175,7 @@
       <c r="D85" s="58"/>
       <c r="E85" s="58"/>
       <c r="F85" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G85" s="58"/>
     </row>
@@ -6187,25 +6190,25 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="67" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B87" s="62" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C87" s="58" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D87" s="63">
         <v>45212</v>
       </c>
       <c r="E87" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F87" s="58" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G87" s="58" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6215,7 +6218,7 @@
       <c r="D88" s="58"/>
       <c r="E88" s="58"/>
       <c r="F88" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G88" s="58"/>
     </row>
@@ -6226,7 +6229,7 @@
       <c r="D89" s="58"/>
       <c r="E89" s="58"/>
       <c r="F89" s="58" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G89" s="58"/>
     </row>
@@ -6237,7 +6240,7 @@
       <c r="D90" s="58"/>
       <c r="E90" s="58"/>
       <c r="F90" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G90" s="58"/>
     </row>
@@ -6248,7 +6251,7 @@
       <c r="D91" s="58"/>
       <c r="E91" s="58"/>
       <c r="F91" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G91" s="58"/>
     </row>
@@ -6263,20 +6266,20 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="67" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B93" s="62" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C93" s="58"/>
       <c r="D93" s="63">
         <v>45212</v>
       </c>
       <c r="E93" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F93" s="58" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="G93" s="58">
         <v>12</v>
@@ -6289,7 +6292,7 @@
       <c r="D94" s="58"/>
       <c r="E94" s="58"/>
       <c r="F94" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G94" s="58"/>
     </row>
@@ -6300,7 +6303,7 @@
       <c r="D95" s="58"/>
       <c r="E95" s="58"/>
       <c r="F95" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G95" s="58"/>
     </row>
@@ -6311,7 +6314,7 @@
       <c r="D96" s="58"/>
       <c r="E96" s="58"/>
       <c r="F96" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G96" s="58"/>
     </row>
@@ -6322,7 +6325,7 @@
       <c r="D97" s="58"/>
       <c r="E97" s="58"/>
       <c r="F97" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G97" s="58"/>
     </row>
@@ -6337,20 +6340,20 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="67" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B99" s="62" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C99" s="58"/>
       <c r="D99" s="63">
         <v>45212</v>
       </c>
       <c r="E99" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F99" s="58" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G99" s="58">
         <v>12</v>
@@ -6363,7 +6366,7 @@
       <c r="D100" s="58"/>
       <c r="E100" s="58"/>
       <c r="F100" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G100" s="58"/>
     </row>
@@ -6374,7 +6377,7 @@
       <c r="D101" s="58"/>
       <c r="E101" s="58"/>
       <c r="F101" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G101" s="58"/>
     </row>
@@ -6385,7 +6388,7 @@
       <c r="D102" s="58"/>
       <c r="E102" s="58"/>
       <c r="F102" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G102" s="58"/>
     </row>
@@ -6396,7 +6399,7 @@
       <c r="D103" s="58"/>
       <c r="E103" s="58"/>
       <c r="F103" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G103" s="58"/>
     </row>
@@ -6411,20 +6414,20 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="67" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B105" s="62" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C105" s="58"/>
       <c r="D105" s="63">
         <v>45212</v>
       </c>
       <c r="E105" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F105" s="58" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="G105" s="58">
         <v>12</v>
@@ -6437,7 +6440,7 @@
       <c r="D106" s="58"/>
       <c r="E106" s="58"/>
       <c r="F106" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G106" s="58"/>
     </row>
@@ -6448,7 +6451,7 @@
       <c r="D107" s="58"/>
       <c r="E107" s="58"/>
       <c r="F107" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G107" s="58"/>
     </row>
@@ -6459,7 +6462,7 @@
       <c r="D108" s="58"/>
       <c r="E108" s="58"/>
       <c r="F108" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G108" s="58"/>
     </row>
@@ -6470,28 +6473,28 @@
       <c r="D109" s="58"/>
       <c r="E109" s="58"/>
       <c r="F109" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G109" s="58"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="65" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B111" s="65" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C111" s="65" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D111" s="66">
         <v>45269</v>
       </c>
       <c r="E111" s="65" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="F111" s="58" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="G111" s="58">
         <v>14</v>
@@ -6504,7 +6507,7 @@
       <c r="D112" s="58"/>
       <c r="E112" s="58"/>
       <c r="F112" s="58" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G112" s="58"/>
     </row>
@@ -6515,7 +6518,7 @@
       <c r="D113" s="58"/>
       <c r="E113" s="58"/>
       <c r="F113" s="58" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="G113" s="58"/>
     </row>
@@ -6530,20 +6533,20 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="67" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B115" s="67" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C115" s="58"/>
       <c r="D115" s="63">
         <v>45275</v>
       </c>
       <c r="E115" s="58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F115" s="58" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="G115" s="58">
         <v>3</v>
@@ -6556,7 +6559,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="58"/>
       <c r="F116" s="64" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G116" s="58"/>
     </row>
@@ -6567,7 +6570,7 @@
       <c r="D117" s="58"/>
       <c r="E117" s="58"/>
       <c r="F117" s="58" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G117" s="58"/>
     </row>
@@ -6578,7 +6581,7 @@
       <c r="D118" s="58"/>
       <c r="E118" s="58"/>
       <c r="F118" s="64" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G118" s="58"/>
     </row>
@@ -6589,7 +6592,7 @@
       <c r="D119" s="58"/>
       <c r="E119" s="58"/>
       <c r="F119" s="58" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="G119" s="58"/>
     </row>
@@ -6609,105 +6612,105 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="4" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="53" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="H3" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I3">
         <v>2004</v>
       </c>
       <c r="M3" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="P3" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="I4" s="58">
         <v>2020</v>
       </c>
       <c r="J4" s="58" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="K4" s="58" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="L4" s="58" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="M4" s="58" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="N4" s="58"/>
       <c r="O4" s="58"/>
@@ -6715,67 +6718,67 @@
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="I5" s="58">
         <v>2016</v>
       </c>
       <c r="J5" s="58" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="K5" s="58"/>
       <c r="L5" s="58" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="M5" s="58" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="N5" s="58"/>
       <c r="O5" s="58"/>
       <c r="P5" s="58" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="I6" s="58">
         <v>2021</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="K6" s="58"/>
       <c r="L6" s="61" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="M6" s="58" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="N6" s="60"/>
       <c r="O6" s="60"/>
@@ -6783,29 +6786,29 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="I7" s="58">
         <v>2015</v>
       </c>
       <c r="J7" s="58" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="K7" s="58"/>
       <c r="L7" s="58" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="M7" s="58"/>
       <c r="N7" s="60"/>
@@ -6814,19 +6817,19 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="I8" s="58">
         <v>2022</v>
@@ -6835,7 +6838,7 @@
       <c r="K8" s="58"/>
       <c r="L8" s="58"/>
       <c r="M8" s="58" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="N8" s="60"/>
       <c r="O8" s="60"/>
@@ -6843,17 +6846,17 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C9">
         <v>7</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="G9" s="58"/>
       <c r="H9" s="58" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="I9" s="58">
         <v>2019</v>
@@ -6862,7 +6865,7 @@
       <c r="K9" s="58"/>
       <c r="L9" s="58"/>
       <c r="M9" s="58" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="N9" s="60"/>
       <c r="O9" s="60"/>
@@ -6870,32 +6873,32 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C10">
         <v>8</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="I10" s="58">
         <v>2023</v>
       </c>
       <c r="J10" s="58" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="K10" s="58"/>
       <c r="L10" s="58" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="N10" s="60"/>
       <c r="O10" s="60"/>
@@ -6903,32 +6906,32 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I11" s="58">
         <v>2021</v>
       </c>
       <c r="J11" s="58" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="K11" s="58"/>
       <c r="L11" s="58" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="N11" s="60"/>
       <c r="O11" s="60"/>
@@ -6936,32 +6939,32 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C12">
         <v>10</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="I12" s="58">
         <v>2023</v>
       </c>
       <c r="J12" s="58" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="K12" s="58"/>
       <c r="L12" s="58" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="N12" s="60"/>
       <c r="O12" s="60"/>
@@ -6969,30 +6972,30 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="I13" s="58">
         <v>2004</v>
       </c>
       <c r="J13" s="58" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="K13" s="58"/>
       <c r="L13" s="58"/>
       <c r="M13" s="58" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="N13" s="60"/>
       <c r="O13" s="60"/>
@@ -7000,32 +7003,32 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="I14" s="58">
         <v>2020</v>
       </c>
       <c r="J14" s="58" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="K14" s="58"/>
       <c r="L14" s="58" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="M14" s="58" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="N14" s="60"/>
       <c r="O14" s="60"/>
@@ -7033,32 +7036,32 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C15">
         <v>13</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="I15" s="58">
         <v>2017</v>
       </c>
       <c r="J15" s="58" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="K15" s="58"/>
       <c r="L15" s="58" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="M15" s="58" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="N15" s="60"/>
       <c r="O15" s="60"/>
@@ -7066,32 +7069,32 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="I16" s="58">
         <v>2023</v>
       </c>
       <c r="J16" s="58" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="K16" s="58"/>
       <c r="L16" s="58" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="M16" s="58" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -7103,6 +7106,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0592d07a-1af2-4331-8b44-ea7e2815515f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a4e2c5e2-cb1f-48cf-889d-fca67caa39a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100019765609737274DAA0BA2312E565507" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="c40fb9a1a6aaae62385305668c4e24bd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0592d07a-1af2-4331-8b44-ea7e2815515f" xmlns:ns3="a4e2c5e2-cb1f-48cf-889d-fca67caa39a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1400a1a61c608a45c948d9a2e55c87f" ns2:_="" ns3:_="">
     <xsd:import namespace="0592d07a-1af2-4331-8b44-ea7e2815515f"/>
@@ -7331,27 +7354,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E9F9AD-9826-4275-8CAC-04A63EEBC2EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0592d07a-1af2-4331-8b44-ea7e2815515f"/>
+    <ds:schemaRef ds:uri="a4e2c5e2-cb1f-48cf-889d-fca67caa39a4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0592d07a-1af2-4331-8b44-ea7e2815515f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a4e2c5e2-cb1f-48cf-889d-fca67caa39a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4849E997-BCEF-45F0-852C-E8B379F267F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37E2A851-32E5-4758-8E8D-87DA26359B5A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7368,23 +7390,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4849E997-BCEF-45F0-852C-E8B379F267F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E9F9AD-9826-4275-8CAC-04A63EEBC2EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0592d07a-1af2-4331-8b44-ea7e2815515f"/>
-    <ds:schemaRef ds:uri="a4e2c5e2-cb1f-48cf-889d-fca67caa39a4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/IEF_Home/UploadedFiles/4_PY_CIRCOMOD_D4.1_v1.0.xlsx
+++ b/IEF_Home/UploadedFiles/4_PY_CIRCOMOD_D4.1_v1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan Pauliuk\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\na1041\Desktop\Uni Stuff\CIRCOMOD\dataValidation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DB6DF5-EA46-4B10-B9FD-47B9CEAC2817}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F427D1-6436-43BE-9E41-B0936C14A62B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15678" windowHeight="5850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15675" windowHeight="5850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -1159,10 +1159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\Te\x\t"/>
-  </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1195,13 +1192,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1282,7 +1272,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1359,12 +1349,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDEDEDE"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1536,10 +1520,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -1548,14 +1532,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,22 +1581,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1620,13 +1604,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1636,45 +1616,37 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="14" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1686,17 +1658,17 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1717,7 +1689,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2038,39 +2010,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.15625" customWidth="1"/>
-    <col min="2" max="2" width="15.83984375" customWidth="1"/>
-    <col min="3" max="3" width="23.15625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.83984375" customWidth="1"/>
-    <col min="5" max="5" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.26171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="3.26171875" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
       <c r="H1" s="21"/>
     </row>
-    <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="76" t="s">
+    <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
         <v>2</v>
@@ -2081,11 +2053,11 @@
       <c r="E3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="68" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -2105,11 +2077,11 @@
       <c r="I4" s="12"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="77"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="41" t="s">
         <v>9</v>
       </c>
@@ -2123,7 +2095,7 @@
       <c r="I5" s="14"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2147,11 +2119,11 @@
       <c r="I6" s="18"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="69" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="41" t="s">
@@ -2173,11 +2145,11 @@
       <c r="I7" s="20"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" s="77"/>
+      <c r="B8" s="67"/>
       <c r="C8" s="41" t="s">
         <v>18</v>
       </c>
@@ -2197,11 +2169,11 @@
       <c r="I8" s="22"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" s="77"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="41" t="s">
         <v>20</v>
       </c>
@@ -2221,11 +2193,11 @@
       <c r="I9" s="22"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="77"/>
+      <c r="B10" s="67"/>
       <c r="C10" s="41" t="s">
         <v>22</v>
       </c>
@@ -2244,16 +2216,16 @@
       <c r="H10" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="70">
+      <c r="I10" s="63">
         <v>40</v>
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="70" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="28" t="s">
@@ -2279,11 +2251,11 @@
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" s="77"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="28" t="s">
         <v>32</v>
       </c>
@@ -2305,11 +2277,11 @@
       <c r="I12" s="30"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" s="77"/>
+      <c r="B13" s="67"/>
       <c r="C13" s="28" t="s">
         <v>36</v>
       </c>
@@ -2331,11 +2303,11 @@
       <c r="I13" s="30"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" s="77"/>
+      <c r="B14" s="67"/>
       <c r="C14" s="28" t="s">
         <v>40</v>
       </c>
@@ -2357,11 +2329,11 @@
       <c r="I14" s="30"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" s="77"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="28" t="s">
         <v>43</v>
       </c>
@@ -2383,11 +2355,11 @@
       <c r="I15" s="30"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="28" t="s">
         <v>47</v>
       </c>
@@ -2409,11 +2381,11 @@
       <c r="I16" s="30"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="28" t="s">
         <v>51</v>
       </c>
@@ -2432,11 +2404,11 @@
       <c r="I17" s="14"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="B18" s="77"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="28" t="s">
         <v>54</v>
       </c>
@@ -2450,11 +2422,11 @@
       <c r="I18" s="14"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19" s="77"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="28" t="s">
         <v>56</v>
       </c>
@@ -2468,11 +2440,11 @@
       <c r="I19" s="14"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" s="77"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="28" t="s">
         <v>58</v>
       </c>
@@ -2486,11 +2458,11 @@
       <c r="I20" s="14"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="71" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="28" t="s">
@@ -2508,11 +2480,11 @@
       <c r="I21" s="34"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="28" t="s">
         <v>62</v>
       </c>
@@ -2524,11 +2496,11 @@
       </c>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23" s="77"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="28" t="s">
         <v>64</v>
       </c>
@@ -2541,11 +2513,11 @@
       <c r="L23" s="1"/>
       <c r="N23" s="35"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" s="77"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="28" t="s">
         <v>65</v>
       </c>
@@ -2560,11 +2532,11 @@
       <c r="N24" s="4"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" s="77"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="28" t="s">
         <v>50</v>
       </c>
@@ -2576,11 +2548,11 @@
       <c r="L25" s="1"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="72" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="36" t="s">
@@ -2597,11 +2569,11 @@
       <c r="L26" s="1"/>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27" s="77"/>
+      <c r="B27" s="67"/>
       <c r="C27" s="36" t="s">
         <v>68</v>
       </c>
@@ -2614,11 +2586,11 @@
       <c r="N27" s="4"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" s="77"/>
+      <c r="B28" s="67"/>
       <c r="C28" s="36" t="s">
         <v>69</v>
       </c>
@@ -2631,11 +2603,11 @@
       <c r="N28" s="4"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="B29" s="77"/>
+      <c r="B29" s="67"/>
       <c r="C29" s="36" t="s">
         <v>70</v>
       </c>
@@ -2648,11 +2620,11 @@
       <c r="N29" s="4"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30" s="77"/>
+      <c r="B30" s="67"/>
       <c r="C30" s="36" t="s">
         <v>71</v>
       </c>
@@ -2664,11 +2636,11 @@
       <c r="H30" s="1"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31" s="77"/>
+      <c r="B31" s="67"/>
       <c r="C31" s="36" t="s">
         <v>72</v>
       </c>
@@ -2680,11 +2652,11 @@
       <c r="H31" s="1"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="B32" s="77"/>
+      <c r="B32" s="67"/>
       <c r="C32" s="36" t="s">
         <v>73</v>
       </c>
@@ -2695,11 +2667,11 @@
       <c r="G32" s="4"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33" s="77"/>
+      <c r="B33" s="67"/>
       <c r="C33" s="36" t="s">
         <v>74</v>
       </c>
@@ -2711,11 +2683,11 @@
       <c r="N33" s="4"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34" s="77"/>
+      <c r="B34" s="67"/>
       <c r="C34" s="36" t="s">
         <v>75</v>
       </c>
@@ -2727,11 +2699,11 @@
       <c r="N34" s="4"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35" s="77"/>
+      <c r="B35" s="67"/>
       <c r="C35" s="36" t="s">
         <v>76</v>
       </c>
@@ -2743,11 +2715,11 @@
       <c r="H35" s="2"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="B36" s="77"/>
+      <c r="B36" s="67"/>
       <c r="C36" s="36" t="s">
         <v>77</v>
       </c>
@@ -2762,11 +2734,11 @@
       <c r="N36" s="4"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="B37" s="77"/>
+      <c r="B37" s="67"/>
       <c r="C37" s="36" t="s">
         <v>78</v>
       </c>
@@ -2779,11 +2751,11 @@
       <c r="G37" s="4"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
-      <c r="B38" s="77"/>
+      <c r="B38" s="67"/>
       <c r="C38" s="36" t="s">
         <v>79</v>
       </c>
@@ -2797,11 +2769,11 @@
       <c r="H38" s="1"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
-      <c r="B39" s="77"/>
+      <c r="B39" s="67"/>
       <c r="C39" s="36" t="s">
         <v>80</v>
       </c>
@@ -2814,11 +2786,11 @@
       <c r="G39" s="4"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
-      <c r="B40" s="77"/>
+      <c r="B40" s="67"/>
       <c r="C40" s="36" t="s">
         <v>81</v>
       </c>
@@ -2831,11 +2803,11 @@
       <c r="G40" s="4"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>38</v>
       </c>
-      <c r="B41" s="77"/>
+      <c r="B41" s="67"/>
       <c r="C41" s="36" t="s">
         <v>82</v>
       </c>
@@ -2848,11 +2820,11 @@
       <c r="G41" s="4"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>39</v>
       </c>
-      <c r="B42" s="77"/>
+      <c r="B42" s="67"/>
       <c r="C42" s="36" t="s">
         <v>83</v>
       </c>
@@ -2865,11 +2837,11 @@
       <c r="G42" s="4"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>40</v>
       </c>
-      <c r="B43" s="77"/>
+      <c r="B43" s="67"/>
       <c r="C43" s="36" t="s">
         <v>84</v>
       </c>
@@ -2885,11 +2857,11 @@
       <c r="P43" s="39"/>
       <c r="Q43" s="45"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>41</v>
       </c>
-      <c r="B44" s="77"/>
+      <c r="B44" s="67"/>
       <c r="C44" s="36" t="s">
         <v>85</v>
       </c>
@@ -2903,11 +2875,11 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>42</v>
       </c>
-      <c r="B45" s="77"/>
+      <c r="B45" s="67"/>
       <c r="C45" s="36" t="s">
         <v>86</v>
       </c>
@@ -2923,11 +2895,11 @@
       <c r="O45" s="3"/>
       <c r="Q45" s="2"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>43</v>
       </c>
-      <c r="B46" s="77"/>
+      <c r="B46" s="67"/>
       <c r="C46" s="36" t="s">
         <v>87</v>
       </c>
@@ -2943,11 +2915,11 @@
       <c r="O46" s="3"/>
       <c r="Q46" s="2"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>44</v>
       </c>
-      <c r="B47" s="77"/>
+      <c r="B47" s="67"/>
       <c r="C47" s="36" t="s">
         <v>88</v>
       </c>
@@ -2962,11 +2934,11 @@
       <c r="O47" s="3"/>
       <c r="Q47" s="2"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>45</v>
       </c>
-      <c r="B48" s="77"/>
+      <c r="B48" s="67"/>
       <c r="C48" s="36" t="s">
         <v>89</v>
       </c>
@@ -2981,11 +2953,11 @@
       <c r="O48" s="3"/>
       <c r="Q48" s="2"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46</v>
       </c>
-      <c r="B49" s="77"/>
+      <c r="B49" s="67"/>
       <c r="C49" s="36" t="s">
         <v>90</v>
       </c>
@@ -2999,11 +2971,11 @@
       <c r="H49" s="3"/>
       <c r="Q49" s="2"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>47</v>
       </c>
-      <c r="B50" s="77"/>
+      <c r="B50" s="67"/>
       <c r="C50" s="28" t="s">
         <v>91</v>
       </c>
@@ -3015,11 +2987,11 @@
       </c>
       <c r="H50" s="47"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>48</v>
       </c>
-      <c r="B51" s="77"/>
+      <c r="B51" s="67"/>
       <c r="C51" s="28" t="s">
         <v>93</v>
       </c>
@@ -3031,11 +3003,11 @@
       </c>
       <c r="H51" s="47"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49</v>
       </c>
-      <c r="B52" s="77"/>
+      <c r="B52" s="67"/>
       <c r="C52" s="28" t="s">
         <v>94</v>
       </c>
@@ -3047,118 +3019,118 @@
       </c>
       <c r="H52" s="47"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" s="83" t="s">
+      <c r="B53" s="73" t="s">
         <v>95</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="71" t="s">
+      <c r="D53" s="64" t="s">
         <v>354</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>51</v>
       </c>
-      <c r="B54" s="77"/>
+      <c r="B54" s="67"/>
       <c r="C54" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="71" t="s">
+      <c r="D54" s="64" t="s">
         <v>341</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>52</v>
       </c>
-      <c r="B55" s="77"/>
+      <c r="B55" s="67"/>
       <c r="C55" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="71" t="s">
+      <c r="D55" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>53</v>
       </c>
-      <c r="B56" s="77"/>
+      <c r="B56" s="67"/>
       <c r="C56" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="D56" s="71" t="s">
+      <c r="D56" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>54</v>
       </c>
-      <c r="B57" s="77"/>
+      <c r="B57" s="67"/>
       <c r="C57" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D57" s="71" t="s">
+      <c r="D57" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>55</v>
       </c>
-      <c r="B58" s="77"/>
+      <c r="B58" s="67"/>
       <c r="C58" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="D58" s="71" t="s">
+      <c r="D58" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>56</v>
       </c>
-      <c r="B59" s="77"/>
+      <c r="B59" s="67"/>
       <c r="C59" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="71" t="s">
+      <c r="D59" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>57</v>
       </c>
-      <c r="B60" s="77"/>
+      <c r="B60" s="67"/>
       <c r="C60" s="41" t="s">
         <v>103</v>
       </c>
@@ -3169,43 +3141,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="74" t="s">
         <v>104</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="D61" s="71" t="s">
+      <c r="D61" s="64" t="s">
         <v>340</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
-      <c r="B62" s="77"/>
+      <c r="B62" s="67"/>
       <c r="C62" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D62" s="72">
+      <c r="D62" s="65">
         <v>45138</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
-      <c r="B63" s="77"/>
+      <c r="B63" s="67"/>
       <c r="C63" s="41" t="s">
         <v>107</v>
       </c>
@@ -3216,11 +3188,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
-      <c r="B64" s="77"/>
+      <c r="B64" s="67"/>
       <c r="C64" s="41" t="s">
         <v>109</v>
       </c>
@@ -3231,11 +3203,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
-      <c r="B65" s="77"/>
+      <c r="B65" s="67"/>
       <c r="C65" s="41" t="s">
         <v>111</v>
       </c>
@@ -3244,11 +3216,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
-      <c r="B66" s="77"/>
+      <c r="B66" s="67"/>
       <c r="C66" s="41" t="s">
         <v>112</v>
       </c>
@@ -3257,11 +3229,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
-      <c r="B67" s="77"/>
+      <c r="B67" s="67"/>
       <c r="C67" s="41" t="s">
         <v>113</v>
       </c>
@@ -3270,11 +3242,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
-      <c r="B68" s="85" t="s">
+      <c r="B68" s="75" t="s">
         <v>114</v>
       </c>
       <c r="C68" s="43" t="s">
@@ -3285,11 +3257,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
-      <c r="B69" s="77"/>
+      <c r="B69" s="67"/>
       <c r="C69" s="43" t="s">
         <v>116</v>
       </c>
@@ -3298,11 +3270,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
-      <c r="B70" s="77"/>
+      <c r="B70" s="67"/>
       <c r="C70" s="43" t="s">
         <v>117</v>
       </c>
@@ -3311,11 +3283,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
-      <c r="B71" s="77"/>
+      <c r="B71" s="67"/>
       <c r="C71" s="43" t="s">
         <v>118</v>
       </c>
@@ -3324,11 +3296,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
-      <c r="B72" s="77"/>
+      <c r="B72" s="67"/>
       <c r="C72" s="44" t="s">
         <v>119</v>
       </c>
@@ -3357,854 +3329,851 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.15625" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.15625" customWidth="1"/>
-    <col min="4" max="5" width="30.578125" customWidth="1"/>
-    <col min="6" max="6" width="28.68359375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.41796875" customWidth="1"/>
-    <col min="8" max="10" width="20.41796875" customWidth="1"/>
-    <col min="11" max="11" width="17.68359375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.41796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.68359375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.68359375" customWidth="1"/>
-    <col min="15" max="15" width="15.15625" style="48" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.68359375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.41796875" customWidth="1"/>
-    <col min="25" max="25" width="13.68359375" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="5" width="30.5703125" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" customWidth="1"/>
+    <col min="25" max="25" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="74" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" t="s">
         <v>339</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" t="s">
         <v>120</v>
       </c>
-      <c r="M1" s="50" t="s">
+      <c r="M1" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="75"/>
-    </row>
-    <row r="2" spans="1:15" s="74" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="59" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>352</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" t="s">
         <v>350</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" t="s">
         <v>351</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="F2" t="s">
         <v>342</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="58">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="58">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2" s="58" t="s">
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="L2" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="75"/>
-    </row>
-    <row r="3" spans="1:15" s="74" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="62" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" t="s">
         <v>356</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" t="s">
         <v>367</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" t="s">
         <v>342</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3">
         <v>0.7</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="58">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="58" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="58" t="s">
+      <c r="K3" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" t="s">
         <v>127</v>
       </c>
-      <c r="M3" s="58" t="s">
+      <c r="M3" t="s">
         <v>129</v>
       </c>
-      <c r="O3" s="75"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="62" t="s">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" t="s">
         <v>357</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" t="s">
         <v>368</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" t="s">
         <v>123</v>
       </c>
       <c r="F4" t="s">
         <v>342</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4">
         <v>28</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" t="s">
         <v>124</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="58" t="s">
+      <c r="J4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="58" t="s">
+      <c r="K4" t="s">
         <v>133</v>
       </c>
-      <c r="L4" s="67" t="s">
+      <c r="L4" t="s">
         <v>132</v>
       </c>
-      <c r="M4" s="58" t="s">
+      <c r="M4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="62" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" t="s">
         <v>357</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" t="s">
         <v>368</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" t="s">
         <v>123</v>
       </c>
       <c r="F5" t="s">
         <v>342</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5">
         <v>28</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" t="s">
         <v>124</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" s="58" t="s">
+      <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="58" t="s">
+      <c r="K5" t="s">
         <v>133</v>
       </c>
-      <c r="L5" s="67" t="s">
+      <c r="L5" t="s">
         <v>135</v>
       </c>
-      <c r="M5" s="58" t="s">
+      <c r="M5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="62" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" t="s">
         <v>357</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" t="s">
         <v>368</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" t="s">
         <v>123</v>
       </c>
       <c r="F6" t="s">
         <v>342</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6">
         <v>28</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" t="s">
         <v>124</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="K6" t="s">
         <v>133</v>
       </c>
-      <c r="L6" s="67" t="s">
+      <c r="L6" t="s">
         <v>137</v>
       </c>
-      <c r="M6" s="58" t="s">
+      <c r="M6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="62" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" t="s">
         <v>358</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" t="s">
         <v>367</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" t="s">
         <v>123</v>
       </c>
       <c r="F7" t="s">
         <v>342</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7">
         <v>99.25</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" t="s">
         <v>124</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" s="58" t="s">
+      <c r="J7" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="58" t="s">
+      <c r="K7" t="s">
         <v>140</v>
       </c>
-      <c r="L7" s="67" t="s">
+      <c r="L7" t="s">
         <v>139</v>
       </c>
-      <c r="M7" s="58" t="s">
+      <c r="M7" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="62" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" t="s">
         <v>359</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" t="s">
         <v>368</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" t="s">
         <v>123</v>
       </c>
       <c r="F8" t="s">
         <v>342</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8">
         <v>30</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" t="s">
         <v>124</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" s="58" t="s">
+      <c r="J8" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="58" t="s">
+      <c r="K8" t="s">
         <v>143</v>
       </c>
-      <c r="L8" s="67" t="s">
+      <c r="L8" t="s">
         <v>142</v>
       </c>
-      <c r="M8" s="58" t="s">
+      <c r="M8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="62" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" t="s">
         <v>368</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" t="s">
         <v>123</v>
       </c>
       <c r="F9" t="s">
         <v>342</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9">
         <v>50</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" t="s">
         <v>124</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" s="58" t="s">
+      <c r="J9" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="58" t="s">
+      <c r="K9" t="s">
         <v>146</v>
       </c>
-      <c r="L9" s="67" t="s">
+      <c r="L9" t="s">
         <v>145</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="M9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="62" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" t="s">
         <v>361</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" t="s">
         <v>131</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" t="s">
         <v>368</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" t="s">
         <v>123</v>
       </c>
       <c r="F10" t="s">
         <v>342</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10">
         <v>95</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" t="s">
         <v>124</v>
       </c>
-      <c r="I10" s="58">
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" s="58" t="s">
+      <c r="J10" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="58" t="s">
+      <c r="K10" t="s">
         <v>149</v>
       </c>
-      <c r="L10" s="67" t="s">
+      <c r="L10" t="s">
         <v>148</v>
       </c>
-      <c r="M10" s="58" t="s">
+      <c r="M10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="62" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" t="s">
         <v>362</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" t="s">
         <v>369</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" t="s">
         <v>123</v>
       </c>
       <c r="F11" t="s">
         <v>342</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11">
         <v>9</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" t="s">
         <v>124</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="58" t="s">
+      <c r="J11" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="58" t="s">
+      <c r="K11" t="s">
         <v>152</v>
       </c>
-      <c r="L11" s="67" t="s">
+      <c r="L11" t="s">
         <v>151</v>
       </c>
-      <c r="M11" s="58" t="s">
+      <c r="M11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="62" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" t="s">
         <v>363</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" t="s">
         <v>371</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" t="s">
         <v>123</v>
       </c>
       <c r="F12" t="s">
         <v>342</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12" s="58">
+      <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12" s="58">
+      <c r="I12">
         <v>1</v>
       </c>
-      <c r="J12" s="58" t="s">
+      <c r="J12" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="58" t="s">
+      <c r="K12" t="s">
         <v>155</v>
       </c>
-      <c r="L12" s="67" t="s">
+      <c r="L12" t="s">
         <v>154</v>
       </c>
-      <c r="M12" s="58" t="s">
+      <c r="M12" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="62" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" t="s">
         <v>364</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" t="s">
         <v>370</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" t="s">
         <v>123</v>
       </c>
       <c r="F13" t="s">
         <v>342</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" s="58">
+      <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="58" t="s">
+      <c r="K13" t="s">
         <v>155</v>
       </c>
-      <c r="L13" s="67" t="s">
+      <c r="L13" t="s">
         <v>157</v>
       </c>
-      <c r="M13" s="58" t="s">
+      <c r="M13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="62" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" t="s">
         <v>364</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" t="s">
         <v>370</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" t="s">
         <v>123</v>
       </c>
       <c r="F14" t="s">
         <v>342</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" s="58">
+      <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" s="58" t="s">
+      <c r="J14" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="58" t="s">
+      <c r="K14" t="s">
         <v>155</v>
       </c>
-      <c r="L14" s="67" t="s">
+      <c r="L14" t="s">
         <v>159</v>
       </c>
-      <c r="M14" s="58" t="s">
+      <c r="M14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="62" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" t="s">
         <v>364</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" t="s">
         <v>370</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" t="s">
         <v>123</v>
       </c>
       <c r="F15" t="s">
         <v>342</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15" s="58">
+      <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" s="58" t="s">
+      <c r="J15" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="58" t="s">
+      <c r="K15" t="s">
         <v>155</v>
       </c>
-      <c r="L15" s="67" t="s">
+      <c r="L15" t="s">
         <v>161</v>
       </c>
-      <c r="M15" s="58" t="s">
+      <c r="M15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="62" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" t="s">
         <v>365</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" t="s">
         <v>357</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" t="s">
         <v>123</v>
       </c>
       <c r="F16" t="s">
         <v>342</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16">
         <v>25</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" t="s">
         <v>124</v>
       </c>
-      <c r="I16" s="58">
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="J16" s="58" t="s">
+      <c r="J16" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="58" t="s">
+      <c r="K16" t="s">
         <v>164</v>
       </c>
-      <c r="L16" s="67" t="s">
+      <c r="L16" t="s">
         <v>163</v>
       </c>
-      <c r="M16" s="58" t="s">
+      <c r="M16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="62" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>165</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" t="s">
         <v>357</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" t="s">
         <v>368</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" t="s">
         <v>123</v>
       </c>
       <c r="F17" t="s">
         <v>342</v>
       </c>
-      <c r="G17" s="68">
+      <c r="G17">
         <v>28</v>
       </c>
-      <c r="H17" s="58" t="s">
+      <c r="H17" t="s">
         <v>124</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17">
         <v>1</v>
       </c>
-      <c r="J17" s="58" t="s">
+      <c r="J17" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="58" t="s">
+      <c r="K17" t="s">
         <v>167</v>
       </c>
-      <c r="L17" s="67" t="s">
+      <c r="L17" t="s">
         <v>166</v>
       </c>
-      <c r="M17" s="58" t="s">
+      <c r="M17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="62" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" t="s">
         <v>169</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" t="s">
         <v>367</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" t="s">
         <v>123</v>
       </c>
       <c r="F18" t="s">
         <v>342</v>
       </c>
-      <c r="G18" s="68">
+      <c r="G18">
         <v>24</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" t="s">
         <v>124</v>
       </c>
-      <c r="I18" s="58">
+      <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18" s="58" t="s">
+      <c r="J18" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="58" t="s">
+      <c r="K18" t="s">
         <v>171</v>
       </c>
-      <c r="L18" s="67" t="s">
+      <c r="L18" t="s">
         <v>170</v>
       </c>
-      <c r="M18" s="58" t="s">
+      <c r="M18" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="62" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" t="s">
         <v>366</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" t="s">
         <v>169</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" t="s">
         <v>367</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" t="s">
         <v>123</v>
       </c>
       <c r="F19" t="s">
         <v>342</v>
       </c>
-      <c r="G19" s="68">
+      <c r="G19">
         <v>23</v>
       </c>
-      <c r="H19" s="58" t="s">
+      <c r="H19" t="s">
         <v>124</v>
       </c>
-      <c r="I19" s="58">
+      <c r="I19">
         <v>1</v>
       </c>
-      <c r="J19" s="58" t="s">
+      <c r="J19" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="58" t="s">
+      <c r="K19" t="s">
         <v>171</v>
       </c>
-      <c r="L19" s="67" t="s">
+      <c r="L19" t="s">
         <v>173</v>
       </c>
-      <c r="M19" s="58" t="s">
+      <c r="M19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="62" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>174</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" t="s">
         <v>366</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" t="s">
         <v>169</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" t="s">
         <v>367</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" t="s">
         <v>123</v>
       </c>
       <c r="F20" t="s">
         <v>342</v>
       </c>
-      <c r="G20" s="68">
+      <c r="G20">
         <v>14</v>
       </c>
-      <c r="H20" s="58" t="s">
+      <c r="H20" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="58">
+      <c r="I20">
         <v>1</v>
       </c>
-      <c r="J20" s="58" t="s">
+      <c r="J20" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="58" t="s">
+      <c r="K20" t="s">
         <v>171</v>
       </c>
-      <c r="L20" s="67" t="s">
+      <c r="L20" t="s">
         <v>175</v>
       </c>
-      <c r="M20" s="58" t="s">
+      <c r="M20" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="65" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>319</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" t="s">
         <v>344</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" t="s">
         <v>177</v>
       </c>
       <c r="E21" t="s">
@@ -4213,41 +4182,39 @@
       <c r="F21" t="s">
         <v>342</v>
       </c>
-      <c r="G21" s="68">
+      <c r="G21">
         <v>95</v>
       </c>
-      <c r="H21" s="58" t="s">
+      <c r="H21" t="s">
         <v>124</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21">
         <v>1</v>
       </c>
-      <c r="J21" s="58" t="s">
+      <c r="J21" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="K21" t="s">
         <v>179</v>
       </c>
-      <c r="L21" s="58" t="s">
+      <c r="L21" t="s">
         <v>178</v>
       </c>
-      <c r="M21" s="58" t="s">
+      <c r="M21" t="s">
         <v>129</v>
       </c>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="65" t="s">
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>320</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" t="s">
         <v>344</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" t="s">
         <v>177</v>
       </c>
       <c r="E22" t="s">
@@ -4256,41 +4223,39 @@
       <c r="F22" t="s">
         <v>342</v>
       </c>
-      <c r="G22" s="68">
+      <c r="G22">
         <v>95</v>
       </c>
-      <c r="H22" s="58" t="s">
+      <c r="H22" t="s">
         <v>124</v>
       </c>
-      <c r="I22" s="58">
+      <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" s="58" t="s">
+      <c r="J22" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="58" t="s">
+      <c r="K22" t="s">
         <v>179</v>
       </c>
-      <c r="L22" s="58" t="s">
+      <c r="L22" t="s">
         <v>178</v>
       </c>
-      <c r="M22" s="58" t="s">
+      <c r="M22" t="s">
         <v>129</v>
       </c>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="65" t="s">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>321</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" t="s">
         <v>176</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" t="s">
         <v>344</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" t="s">
         <v>177</v>
       </c>
       <c r="E23" t="s">
@@ -4299,41 +4264,39 @@
       <c r="F23" t="s">
         <v>342</v>
       </c>
-      <c r="G23" s="68">
+      <c r="G23">
         <v>95</v>
       </c>
-      <c r="H23" s="58" t="s">
+      <c r="H23" t="s">
         <v>124</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23" s="58" t="s">
+      <c r="J23" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="58" t="s">
+      <c r="K23" t="s">
         <v>180</v>
       </c>
-      <c r="L23" s="58" t="s">
+      <c r="L23" t="s">
         <v>178</v>
       </c>
-      <c r="M23" s="58" t="s">
+      <c r="M23" t="s">
         <v>129</v>
       </c>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="65" t="s">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>322</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" t="s">
         <v>176</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" t="s">
         <v>344</v>
       </c>
-      <c r="D24" s="58" t="s">
+      <c r="D24" t="s">
         <v>177</v>
       </c>
       <c r="E24" t="s">
@@ -4342,41 +4305,39 @@
       <c r="F24" t="s">
         <v>342</v>
       </c>
-      <c r="G24" s="68">
+      <c r="G24">
         <v>95</v>
       </c>
-      <c r="H24" s="58" t="s">
+      <c r="H24" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="58">
+      <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" s="58" t="s">
+      <c r="J24" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="58" t="s">
+      <c r="K24" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="58" t="s">
+      <c r="L24" t="s">
         <v>178</v>
       </c>
-      <c r="M24" s="58" t="s">
+      <c r="M24" t="s">
         <v>129</v>
       </c>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="65" t="s">
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>323</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" t="s">
         <v>344</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="D25" t="s">
         <v>177</v>
       </c>
       <c r="E25" t="s">
@@ -4385,41 +4346,39 @@
       <c r="F25" t="s">
         <v>342</v>
       </c>
-      <c r="G25" s="68">
+      <c r="G25">
         <v>95</v>
       </c>
-      <c r="H25" s="58" t="s">
+      <c r="H25" t="s">
         <v>124</v>
       </c>
-      <c r="I25" s="58">
+      <c r="I25">
         <v>1</v>
       </c>
-      <c r="J25" s="58" t="s">
+      <c r="J25" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="K25" t="s">
         <v>182</v>
       </c>
-      <c r="L25" s="58" t="s">
+      <c r="L25" t="s">
         <v>178</v>
       </c>
-      <c r="M25" s="58" t="s">
+      <c r="M25" t="s">
         <v>129</v>
       </c>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="65" t="s">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>324</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" t="s">
         <v>344</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="D26" t="s">
         <v>177</v>
       </c>
       <c r="E26" t="s">
@@ -4428,39 +4387,36 @@
       <c r="F26" t="s">
         <v>342</v>
       </c>
-      <c r="G26" s="68">
+      <c r="G26">
         <v>95</v>
       </c>
-      <c r="H26" s="58" t="s">
+      <c r="H26" t="s">
         <v>124</v>
       </c>
-      <c r="I26" s="58">
+      <c r="I26">
         <v>1</v>
       </c>
-      <c r="J26" s="58" t="s">
+      <c r="J26" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58" t="s">
+      <c r="L26" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="58" t="s">
+      <c r="M26" t="s">
         <v>129</v>
       </c>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="65" t="s">
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" t="s">
         <v>176</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" t="s">
         <v>344</v>
       </c>
-      <c r="D27" s="58" t="s">
+      <c r="D27" t="s">
         <v>177</v>
       </c>
       <c r="E27" t="s">
@@ -4469,41 +4425,39 @@
       <c r="F27" t="s">
         <v>342</v>
       </c>
-      <c r="G27" s="68">
+      <c r="G27">
         <v>95</v>
       </c>
-      <c r="H27" s="58" t="s">
+      <c r="H27" t="s">
         <v>124</v>
       </c>
-      <c r="I27" s="58">
+      <c r="I27">
         <v>1</v>
       </c>
-      <c r="J27" s="58" t="s">
+      <c r="J27" t="s">
         <v>37</v>
       </c>
-      <c r="K27" s="58" t="s">
+      <c r="K27" t="s">
         <v>182</v>
       </c>
-      <c r="L27" s="58" t="s">
+      <c r="L27" t="s">
         <v>178</v>
       </c>
-      <c r="M27" s="58" t="s">
+      <c r="M27" t="s">
         <v>129</v>
       </c>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="65" t="s">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>326</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" t="s">
         <v>176</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" t="s">
         <v>344</v>
       </c>
-      <c r="D28" s="58" t="s">
+      <c r="D28" t="s">
         <v>177</v>
       </c>
       <c r="E28" t="s">
@@ -4512,41 +4466,39 @@
       <c r="F28" t="s">
         <v>342</v>
       </c>
-      <c r="G28" s="68">
+      <c r="G28">
         <v>95</v>
       </c>
-      <c r="H28" s="58" t="s">
+      <c r="H28" t="s">
         <v>124</v>
       </c>
-      <c r="I28" s="58">
+      <c r="I28">
         <v>1</v>
       </c>
-      <c r="J28" s="58" t="s">
+      <c r="J28" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="58" t="s">
+      <c r="K28" t="s">
         <v>183</v>
       </c>
-      <c r="L28" s="58" t="s">
+      <c r="L28" t="s">
         <v>178</v>
       </c>
-      <c r="M28" s="58" t="s">
+      <c r="M28" t="s">
         <v>129</v>
       </c>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="65" t="s">
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>327</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" t="s">
         <v>176</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" t="s">
         <v>344</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" t="s">
         <v>177</v>
       </c>
       <c r="E29" t="s">
@@ -4555,41 +4507,39 @@
       <c r="F29" t="s">
         <v>342</v>
       </c>
-      <c r="G29" s="68">
+      <c r="G29">
         <v>95</v>
       </c>
-      <c r="H29" s="58" t="s">
+      <c r="H29" t="s">
         <v>124</v>
       </c>
-      <c r="I29" s="58">
+      <c r="I29">
         <v>1</v>
       </c>
-      <c r="J29" s="58" t="s">
+      <c r="J29" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="58" t="s">
+      <c r="K29" t="s">
         <v>183</v>
       </c>
-      <c r="L29" s="58" t="s">
+      <c r="L29" t="s">
         <v>178</v>
       </c>
-      <c r="M29" s="58" t="s">
+      <c r="M29" t="s">
         <v>129</v>
       </c>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="65" t="s">
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>328</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" t="s">
         <v>344</v>
       </c>
-      <c r="D30" s="58" t="s">
+      <c r="D30" t="s">
         <v>177</v>
       </c>
       <c r="E30" t="s">
@@ -4598,41 +4548,39 @@
       <c r="F30" t="s">
         <v>342</v>
       </c>
-      <c r="G30" s="68">
+      <c r="G30">
         <v>95</v>
       </c>
-      <c r="H30" s="58" t="s">
+      <c r="H30" t="s">
         <v>124</v>
       </c>
-      <c r="I30" s="58">
+      <c r="I30">
         <v>1</v>
       </c>
-      <c r="J30" s="58" t="s">
+      <c r="J30" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="58" t="s">
+      <c r="K30" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="58" t="s">
+      <c r="L30" t="s">
         <v>178</v>
       </c>
-      <c r="M30" s="58" t="s">
+      <c r="M30" t="s">
         <v>129</v>
       </c>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="65" t="s">
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>329</v>
       </c>
-      <c r="B31" s="58" t="s">
+      <c r="B31" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" t="s">
         <v>344</v>
       </c>
-      <c r="D31" s="58" t="s">
+      <c r="D31" t="s">
         <v>177</v>
       </c>
       <c r="E31" t="s">
@@ -4641,41 +4589,39 @@
       <c r="F31" t="s">
         <v>342</v>
       </c>
-      <c r="G31" s="68">
+      <c r="G31">
         <v>95</v>
       </c>
-      <c r="H31" s="58" t="s">
+      <c r="H31" t="s">
         <v>124</v>
       </c>
-      <c r="I31" s="58">
+      <c r="I31">
         <v>1</v>
       </c>
-      <c r="J31" s="58" t="s">
+      <c r="J31" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="58" t="s">
+      <c r="K31" t="s">
         <v>182</v>
       </c>
-      <c r="L31" s="58" t="s">
+      <c r="L31" t="s">
         <v>178</v>
       </c>
-      <c r="M31" s="58" t="s">
+      <c r="M31" t="s">
         <v>129</v>
       </c>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="65" t="s">
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>330</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" t="s">
         <v>344</v>
       </c>
-      <c r="D32" s="58" t="s">
+      <c r="D32" t="s">
         <v>177</v>
       </c>
       <c r="E32" t="s">
@@ -4684,39 +4630,36 @@
       <c r="F32" t="s">
         <v>342</v>
       </c>
-      <c r="G32" s="68">
+      <c r="G32">
         <v>95</v>
       </c>
-      <c r="H32" s="58" t="s">
+      <c r="H32" t="s">
         <v>124</v>
       </c>
-      <c r="I32" s="58">
+      <c r="I32">
         <v>1</v>
       </c>
-      <c r="J32" s="58" t="s">
+      <c r="J32" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58" t="s">
+      <c r="L32" t="s">
         <v>178</v>
       </c>
-      <c r="M32" s="58" t="s">
+      <c r="M32" t="s">
         <v>129</v>
       </c>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="65" t="s">
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>331</v>
       </c>
-      <c r="B33" s="58" t="s">
+      <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="58" t="s">
+      <c r="D33" t="s">
         <v>177</v>
       </c>
       <c r="E33" t="s">
@@ -4725,39 +4668,36 @@
       <c r="F33" t="s">
         <v>342</v>
       </c>
-      <c r="G33" s="68">
+      <c r="G33">
         <v>95</v>
       </c>
-      <c r="H33" s="58" t="s">
+      <c r="H33" t="s">
         <v>124</v>
       </c>
-      <c r="I33" s="58">
+      <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" s="58" t="s">
+      <c r="J33" t="s">
         <v>37</v>
       </c>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58" t="s">
+      <c r="L33" t="s">
         <v>178</v>
       </c>
-      <c r="M33" s="58" t="s">
+      <c r="M33" t="s">
         <v>129</v>
       </c>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="65" t="s">
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>332</v>
       </c>
-      <c r="B34" s="58" t="s">
+      <c r="B34" t="s">
         <v>176</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" t="s">
         <v>344</v>
       </c>
-      <c r="D34" s="58" t="s">
+      <c r="D34" t="s">
         <v>177</v>
       </c>
       <c r="E34" t="s">
@@ -4766,39 +4706,36 @@
       <c r="F34" t="s">
         <v>342</v>
       </c>
-      <c r="G34" s="68">
+      <c r="G34">
         <v>95</v>
       </c>
-      <c r="H34" s="58" t="s">
+      <c r="H34" t="s">
         <v>124</v>
       </c>
-      <c r="I34" s="58">
+      <c r="I34">
         <v>1</v>
       </c>
-      <c r="J34" s="58" t="s">
+      <c r="J34" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58" t="s">
+      <c r="L34" t="s">
         <v>178</v>
       </c>
-      <c r="M34" s="58" t="s">
+      <c r="M34" t="s">
         <v>129</v>
       </c>
-      <c r="N34" s="58"/>
-      <c r="O34" s="58"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="65" t="s">
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>333</v>
       </c>
-      <c r="B35" s="58" t="s">
+      <c r="B35" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" t="s">
         <v>344</v>
       </c>
-      <c r="D35" s="58" t="s">
+      <c r="D35" t="s">
         <v>177</v>
       </c>
       <c r="E35" t="s">
@@ -4807,41 +4744,39 @@
       <c r="F35" t="s">
         <v>342</v>
       </c>
-      <c r="G35" s="68">
+      <c r="G35">
         <v>95</v>
       </c>
-      <c r="H35" s="58" t="s">
+      <c r="H35" t="s">
         <v>124</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35">
         <v>1</v>
       </c>
-      <c r="J35" s="58" t="s">
+      <c r="J35" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="58" t="s">
+      <c r="K35" t="s">
         <v>183</v>
       </c>
-      <c r="L35" s="58" t="s">
+      <c r="L35" t="s">
         <v>178</v>
       </c>
-      <c r="M35" s="58" t="s">
+      <c r="M35" t="s">
         <v>129</v>
       </c>
-      <c r="N35" s="58"/>
-      <c r="O35" s="58"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="65" t="s">
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>334</v>
       </c>
-      <c r="B36" s="58" t="s">
+      <c r="B36" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" t="s">
         <v>344</v>
       </c>
-      <c r="D36" s="58" t="s">
+      <c r="D36" t="s">
         <v>177</v>
       </c>
       <c r="E36" t="s">
@@ -4850,41 +4785,39 @@
       <c r="F36" t="s">
         <v>342</v>
       </c>
-      <c r="G36" s="68">
+      <c r="G36">
         <v>95</v>
       </c>
-      <c r="H36" s="58" t="s">
+      <c r="H36" t="s">
         <v>124</v>
       </c>
-      <c r="I36" s="58">
+      <c r="I36">
         <v>1</v>
       </c>
-      <c r="J36" s="58" t="s">
+      <c r="J36" t="s">
         <v>37</v>
       </c>
-      <c r="K36" s="58" t="s">
+      <c r="K36" t="s">
         <v>183</v>
       </c>
-      <c r="L36" s="58" t="s">
+      <c r="L36" t="s">
         <v>178</v>
       </c>
-      <c r="M36" s="58" t="s">
+      <c r="M36" t="s">
         <v>129</v>
       </c>
-      <c r="N36" s="58"/>
-      <c r="O36" s="58"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="65" t="s">
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>335</v>
       </c>
-      <c r="B37" s="58" t="s">
+      <c r="B37" t="s">
         <v>176</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" t="s">
         <v>344</v>
       </c>
-      <c r="D37" s="58" t="s">
+      <c r="D37" t="s">
         <v>177</v>
       </c>
       <c r="E37" t="s">
@@ -4893,41 +4826,39 @@
       <c r="F37" t="s">
         <v>342</v>
       </c>
-      <c r="G37" s="68">
+      <c r="G37">
         <v>95</v>
       </c>
-      <c r="H37" s="58" t="s">
+      <c r="H37" t="s">
         <v>124</v>
       </c>
-      <c r="I37" s="58">
+      <c r="I37">
         <v>1</v>
       </c>
-      <c r="J37" s="58" t="s">
+      <c r="J37" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="58" t="s">
+      <c r="K37" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="58" t="s">
+      <c r="L37" t="s">
         <v>178</v>
       </c>
-      <c r="M37" s="58" t="s">
+      <c r="M37" t="s">
         <v>129</v>
       </c>
-      <c r="N37" s="58"/>
-      <c r="O37" s="58"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="65" t="s">
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>336</v>
       </c>
-      <c r="B38" s="58" t="s">
+      <c r="B38" t="s">
         <v>176</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" t="s">
         <v>344</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="D38" t="s">
         <v>177</v>
       </c>
       <c r="E38" t="s">
@@ -4936,41 +4867,39 @@
       <c r="F38" t="s">
         <v>342</v>
       </c>
-      <c r="G38" s="68">
+      <c r="G38">
         <v>95</v>
       </c>
-      <c r="H38" s="58" t="s">
+      <c r="H38" t="s">
         <v>124</v>
       </c>
-      <c r="I38" s="58">
+      <c r="I38">
         <v>1</v>
       </c>
-      <c r="J38" s="58" t="s">
+      <c r="J38" t="s">
         <v>37</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="K38" t="s">
         <v>182</v>
       </c>
-      <c r="L38" s="58" t="s">
+      <c r="L38" t="s">
         <v>178</v>
       </c>
-      <c r="M38" s="58" t="s">
+      <c r="M38" t="s">
         <v>129</v>
       </c>
-      <c r="N38" s="58"/>
-      <c r="O38" s="58"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="65" t="s">
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>337</v>
       </c>
-      <c r="B39" s="58" t="s">
+      <c r="B39" t="s">
         <v>176</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" t="s">
         <v>344</v>
       </c>
-      <c r="D39" s="58" t="s">
+      <c r="D39" t="s">
         <v>177</v>
       </c>
       <c r="E39" t="s">
@@ -4979,39 +4908,36 @@
       <c r="F39" t="s">
         <v>342</v>
       </c>
-      <c r="G39" s="68">
+      <c r="G39">
         <v>95</v>
       </c>
-      <c r="H39" s="58" t="s">
+      <c r="H39" t="s">
         <v>124</v>
       </c>
-      <c r="I39" s="58">
+      <c r="I39">
         <v>1</v>
       </c>
-      <c r="J39" s="58" t="s">
+      <c r="J39" t="s">
         <v>37</v>
       </c>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58" t="s">
+      <c r="L39" t="s">
         <v>178</v>
       </c>
-      <c r="M39" s="58" t="s">
+      <c r="M39" t="s">
         <v>129</v>
       </c>
-      <c r="N39" s="58"/>
-      <c r="O39" s="58"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="65" t="s">
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>338</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" t="s">
         <v>344</v>
       </c>
-      <c r="D40" s="58" t="s">
+      <c r="D40" t="s">
         <v>177</v>
       </c>
       <c r="E40" t="s">
@@ -5020,74 +4946,65 @@
       <c r="F40" t="s">
         <v>342</v>
       </c>
-      <c r="G40" s="68">
+      <c r="G40">
         <v>95</v>
       </c>
-      <c r="H40" s="58" t="s">
+      <c r="H40" t="s">
         <v>124</v>
       </c>
-      <c r="I40" s="58">
+      <c r="I40">
         <v>1</v>
       </c>
-      <c r="J40" s="58" t="s">
+      <c r="J40" t="s">
         <v>37</v>
       </c>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58" t="s">
+      <c r="L40" t="s">
         <v>178</v>
       </c>
-      <c r="M40" s="58" t="s">
+      <c r="M40" t="s">
         <v>129</v>
       </c>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="67" t="s">
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>184</v>
       </c>
-      <c r="B41" s="58" t="s">
+      <c r="B41" t="s">
         <v>364</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" t="s">
         <v>131</v>
       </c>
-      <c r="D41" s="58" t="s">
+      <c r="D41" t="s">
         <v>370</v>
       </c>
-      <c r="E41" s="58" t="s">
+      <c r="E41" t="s">
         <v>123</v>
       </c>
       <c r="F41" t="s">
         <v>342</v>
       </c>
-      <c r="G41" s="68">
+      <c r="G41">
         <v>1</v>
       </c>
-      <c r="H41" s="58">
+      <c r="H41">
         <v>1</v>
       </c>
-      <c r="I41" s="58">
+      <c r="I41">
         <v>1</v>
       </c>
-      <c r="J41" s="58" t="s">
+      <c r="J41" t="s">
         <v>37</v>
       </c>
-      <c r="K41" s="58" t="s">
+      <c r="K41" t="s">
         <v>155</v>
       </c>
-      <c r="L41" s="67" t="s">
+      <c r="L41" t="s">
         <v>185</v>
       </c>
-      <c r="M41" s="58" t="s">
+      <c r="M41" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="G42" s="69"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="G43" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -5098,1503 +5015,1503 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:G119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.68359375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.26171875" customWidth="1"/>
-    <col min="3" max="3" width="26.578125" customWidth="1"/>
-    <col min="4" max="4" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="65.83984375" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="55.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="54" t="s">
+    <row r="2" spans="1:7" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="51" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="67" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="58">
         <v>45212</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="54">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="64" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G4" s="58"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="58"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58" t="s">
+      <c r="G4" s="54"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="58"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="64" t="s">
+      <c r="G5" s="54"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G6" s="58"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58" t="s">
+      <c r="G6" s="54"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="58"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="67" t="s">
+      <c r="G7" s="54"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="58">
         <v>45212</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="64" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="58"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58" t="s">
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G11" s="58"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="64" t="s">
+      <c r="G11" s="54"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G12" s="58"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58" t="s">
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G13" s="58"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="67" t="s">
+      <c r="G13" s="54"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="58">
         <v>45212</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="64" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G16" s="58"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58" t="s">
+      <c r="G16" s="54"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G17" s="58"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="64" t="s">
+      <c r="G17" s="54"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G18" s="58"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58" t="s">
+      <c r="G18" s="54"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G19" s="58"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="67" t="s">
+      <c r="G19" s="54"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D21" s="58">
         <v>45212</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="64" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G22" s="58"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58" t="s">
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G23" s="58"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="64" t="s">
+      <c r="G23" s="54"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G24" s="58"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58" t="s">
+      <c r="G24" s="54"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G25" s="58"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="58"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58">
+      <c r="G25" s="54"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="67" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="58">
         <v>45212</v>
       </c>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="G27" s="58"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="58"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="64" t="s">
+      <c r="G27" s="54"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G28" s="58"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="58"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58" t="s">
+      <c r="G28" s="54"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="54"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="58"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="64" t="s">
+      <c r="G29" s="54"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="58"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="58"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58" t="s">
+      <c r="G30" s="54"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G31" s="58"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="67" t="s">
+      <c r="G31" s="54"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="58">
         <v>45212</v>
       </c>
-      <c r="E33" s="58" t="s">
+      <c r="E33" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F33" s="58" t="s">
+      <c r="F33" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="58" t="s">
+      <c r="G33" s="54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="64" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G34" s="58"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58" t="s">
+      <c r="G34" s="54"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="54"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="G35" s="58"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="64" t="s">
+      <c r="G35" s="54"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G36" s="58"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58" t="s">
+      <c r="G36" s="54"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G37" s="58"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="58"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="67" t="s">
+      <c r="G37" s="54"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D39" s="63">
+      <c r="D39" s="58">
         <v>45212</v>
       </c>
-      <c r="E39" s="58" t="s">
+      <c r="E39" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="G39" s="58" t="s">
+      <c r="G39" s="54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="64" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="54"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G40" s="58"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58" t="s">
+      <c r="G40" s="54"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="G41" s="58"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="64" t="s">
+      <c r="G41" s="54"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G42" s="58"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58" t="s">
+      <c r="G42" s="54"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G43" s="58"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="67" t="s">
+      <c r="G43" s="54"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="B45" s="62" t="s">
+      <c r="B45" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="D45" s="63">
+      <c r="D45" s="58">
         <v>45212</v>
       </c>
-      <c r="E45" s="58" t="s">
+      <c r="E45" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F45" s="58" t="s">
+      <c r="F45" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="G45" s="58" t="s">
+      <c r="G45" s="54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="64" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G46" s="58"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58" t="s">
+      <c r="G46" s="54"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="58"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="64" t="s">
+      <c r="G47" s="54"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G48" s="58"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58" t="s">
+      <c r="G48" s="54"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G49" s="58"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="67" t="s">
+      <c r="G49" s="54"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="62" t="s">
+      <c r="B51" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="D51" s="63">
+      <c r="D51" s="58">
         <v>45212</v>
       </c>
-      <c r="E51" s="58" t="s">
+      <c r="E51" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F51" s="58" t="s">
+      <c r="F51" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="G51" s="58">
+      <c r="G51" s="54">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="64" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="54"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G52" s="58"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58" t="s">
+      <c r="G52" s="54"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G53" s="58"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="58"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="64" t="s">
+      <c r="G53" s="54"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G54" s="58"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58" t="s">
+      <c r="G54" s="54"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G55" s="58"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="58"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="67" t="s">
+      <c r="G55" s="54"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="B57" s="62" t="s">
+      <c r="B57" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="D57" s="63">
+      <c r="D57" s="58">
         <v>45212</v>
       </c>
-      <c r="E57" s="58" t="s">
+      <c r="E57" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F57" s="58" t="s">
+      <c r="F57" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="G57" s="58">
+      <c r="G57" s="54">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="64" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G58" s="58"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="58"/>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58" t="s">
+      <c r="G58" s="54"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="54"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G59" s="58"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="58"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="64" t="s">
+      <c r="G59" s="54"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="54"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G60" s="58"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="58"/>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58" t="s">
+      <c r="G60" s="54"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="54"/>
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G61" s="58"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="58"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="67" t="s">
+      <c r="G61" s="54"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="54"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="B63" s="62" t="s">
+      <c r="B63" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="C63" s="58"/>
-      <c r="D63" s="63">
+      <c r="C63" s="54"/>
+      <c r="D63" s="58">
         <v>45212</v>
       </c>
-      <c r="E63" s="58" t="s">
+      <c r="E63" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F63" s="58" t="s">
+      <c r="F63" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="G63" s="58">
+      <c r="G63" s="54">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="58"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="64" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="54"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G64" s="58"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="58"/>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58" t="s">
+      <c r="G64" s="54"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="54"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G65" s="58"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="58"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="64" t="s">
+      <c r="G65" s="54"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="54"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G66" s="58"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="58"/>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58" t="s">
+      <c r="G66" s="54"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="54"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G67" s="58"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="67" t="s">
+      <c r="G67" s="54"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="54"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="62" t="s">
+      <c r="B69" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="C69" s="58"/>
-      <c r="D69" s="63">
+      <c r="C69" s="54"/>
+      <c r="D69" s="58">
         <v>45212</v>
       </c>
-      <c r="E69" s="58" t="s">
+      <c r="E69" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F69" s="58" t="s">
+      <c r="F69" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="G69" s="58">
+      <c r="G69" s="54">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="58"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="64" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="54"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G70" s="58"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58" t="s">
+      <c r="G70" s="54"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="54"/>
+      <c r="B71" s="54"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G71" s="58"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="58"/>
-      <c r="B72" s="58"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="64" t="s">
+      <c r="G71" s="54"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="54"/>
+      <c r="B72" s="54"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G72" s="58"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="58"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58" t="s">
+      <c r="G72" s="54"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="54"/>
+      <c r="B73" s="54"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G73" s="58"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="58"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="67" t="s">
+      <c r="G73" s="54"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="54"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="B75" s="62" t="s">
+      <c r="B75" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C75" s="58"/>
-      <c r="D75" s="63">
+      <c r="C75" s="54"/>
+      <c r="D75" s="58">
         <v>45212</v>
       </c>
-      <c r="E75" s="58" t="s">
+      <c r="E75" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F75" s="58" t="s">
+      <c r="F75" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="G75" s="58">
+      <c r="G75" s="54">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="58"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="58"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="64" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="54"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G76" s="58"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="58"/>
-      <c r="B77" s="58"/>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58" t="s">
+      <c r="G76" s="54"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="54"/>
+      <c r="B77" s="54"/>
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G77" s="58"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="58"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="64" t="s">
+      <c r="G77" s="54"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="54"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G78" s="58"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="58"/>
-      <c r="B79" s="58"/>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="58" t="s">
+      <c r="G78" s="54"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G79" s="58"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="58"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="58"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="67" t="s">
+      <c r="G79" s="54"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="62" t="s">
+      <c r="B81" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="58" t="s">
+      <c r="C81" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="D81" s="63">
+      <c r="D81" s="58">
         <v>45212</v>
       </c>
-      <c r="E81" s="58" t="s">
+      <c r="E81" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F81" s="58" t="s">
+      <c r="F81" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="G81" s="58" t="s">
+      <c r="G81" s="54" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="58"/>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="64" t="s">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="54"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G82" s="58"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58" t="s">
+      <c r="G82" s="54"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="54"/>
+      <c r="B83" s="54"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G83" s="58"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="58"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
-      <c r="E84" s="58"/>
-      <c r="F84" s="64" t="s">
+      <c r="G83" s="54"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="54"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G84" s="58"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58" t="s">
+      <c r="G84" s="54"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="54"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="54"/>
+      <c r="D85" s="54"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G85" s="58"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="58"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="67" t="s">
+      <c r="G85" s="54"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="54"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="54"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="62" t="s">
+      <c r="B87" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="C87" s="58" t="s">
+      <c r="C87" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="D87" s="63">
+      <c r="D87" s="58">
         <v>45212</v>
       </c>
-      <c r="E87" s="58" t="s">
+      <c r="E87" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F87" s="58" t="s">
+      <c r="F87" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="G87" s="58" t="s">
+      <c r="G87" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="58"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="58"/>
-      <c r="F88" s="64" t="s">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="54"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G88" s="58"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="58"/>
-      <c r="B89" s="58"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58" t="s">
+      <c r="G88" s="54"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="54"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="G89" s="58"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="58"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="64" t="s">
+      <c r="G89" s="54"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="54"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G90" s="58"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="58"/>
-      <c r="B91" s="58"/>
-      <c r="C91" s="58"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58" t="s">
+      <c r="G90" s="54"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="54"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="54"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G91" s="58"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="58"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="58"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="67" t="s">
+      <c r="G91" s="54"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="54"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="B93" s="62" t="s">
+      <c r="B93" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="C93" s="58"/>
-      <c r="D93" s="63">
+      <c r="C93" s="54"/>
+      <c r="D93" s="58">
         <v>45212</v>
       </c>
-      <c r="E93" s="58" t="s">
+      <c r="E93" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F93" s="58" t="s">
+      <c r="F93" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="G93" s="58">
+      <c r="G93" s="54">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="58"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="64" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="54"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G94" s="58"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="58"/>
-      <c r="B95" s="58"/>
-      <c r="C95" s="58"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58" t="s">
+      <c r="G94" s="54"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="54"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G95" s="58"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="58"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="58"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="64" t="s">
+      <c r="G95" s="54"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="54"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="54"/>
+      <c r="D96" s="54"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G96" s="58"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="58"/>
-      <c r="B97" s="58"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58" t="s">
+      <c r="G96" s="54"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="54"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="54"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G97" s="58"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="58"/>
-      <c r="B98" s="58"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="67" t="s">
+      <c r="G97" s="54"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="54"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="62" t="s">
         <v>173</v>
       </c>
-      <c r="B99" s="62" t="s">
+      <c r="B99" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="C99" s="58"/>
-      <c r="D99" s="63">
+      <c r="C99" s="54"/>
+      <c r="D99" s="58">
         <v>45212</v>
       </c>
-      <c r="E99" s="58" t="s">
+      <c r="E99" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F99" s="58" t="s">
+      <c r="F99" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="G99" s="58">
+      <c r="G99" s="54">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="58"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="58"/>
-      <c r="E100" s="58"/>
-      <c r="F100" s="64" t="s">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="54"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G100" s="58"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="58"/>
-      <c r="B101" s="58"/>
-      <c r="C101" s="58"/>
-      <c r="D101" s="58"/>
-      <c r="E101" s="58"/>
-      <c r="F101" s="58" t="s">
+      <c r="G100" s="54"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="54"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="54"/>
+      <c r="D101" s="54"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G101" s="58"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="58"/>
-      <c r="B102" s="58"/>
-      <c r="C102" s="58"/>
-      <c r="D102" s="58"/>
-      <c r="E102" s="58"/>
-      <c r="F102" s="64" t="s">
+      <c r="G101" s="54"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="54"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G102" s="58"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="58"/>
-      <c r="B103" s="58"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
-      <c r="E103" s="58"/>
-      <c r="F103" s="58" t="s">
+      <c r="G102" s="54"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="54"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="54"/>
+      <c r="D103" s="54"/>
+      <c r="E103" s="54"/>
+      <c r="F103" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G103" s="58"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="58"/>
-      <c r="B104" s="58"/>
-      <c r="C104" s="58"/>
-      <c r="D104" s="58"/>
-      <c r="E104" s="58"/>
-      <c r="F104" s="58"/>
-      <c r="G104" s="58"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="67" t="s">
+      <c r="G103" s="54"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="54"/>
+      <c r="B104" s="54"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="B105" s="62" t="s">
+      <c r="B105" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="C105" s="58"/>
-      <c r="D105" s="63">
+      <c r="C105" s="54"/>
+      <c r="D105" s="58">
         <v>45212</v>
       </c>
-      <c r="E105" s="58" t="s">
+      <c r="E105" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F105" s="58" t="s">
+      <c r="F105" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="G105" s="58">
+      <c r="G105" s="54">
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="58"/>
-      <c r="B106" s="58"/>
-      <c r="C106" s="58"/>
-      <c r="D106" s="58"/>
-      <c r="E106" s="58"/>
-      <c r="F106" s="64" t="s">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="54"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="54"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G106" s="58"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="58"/>
-      <c r="B107" s="58"/>
-      <c r="C107" s="58"/>
-      <c r="D107" s="58"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="58" t="s">
+      <c r="G106" s="54"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="54"/>
+      <c r="B107" s="54"/>
+      <c r="C107" s="54"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G107" s="58"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="58"/>
-      <c r="B108" s="58"/>
-      <c r="C108" s="58"/>
-      <c r="D108" s="58"/>
-      <c r="E108" s="58"/>
-      <c r="F108" s="64" t="s">
+      <c r="G107" s="54"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="54"/>
+      <c r="B108" s="54"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="54"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G108" s="58"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="58"/>
-      <c r="B109" s="58"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
-      <c r="E109" s="58"/>
-      <c r="F109" s="58" t="s">
+      <c r="G108" s="54"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="54"/>
+      <c r="B109" s="54"/>
+      <c r="C109" s="54"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G109" s="58"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="65" t="s">
+      <c r="G109" s="54"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="B111" s="65" t="s">
+      <c r="B111" s="60" t="s">
         <v>225</v>
       </c>
-      <c r="C111" s="65" t="s">
+      <c r="C111" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="61">
         <v>45269</v>
       </c>
-      <c r="E111" s="65" t="s">
+      <c r="E111" s="60" t="s">
         <v>193</v>
       </c>
-      <c r="F111" s="58" t="s">
+      <c r="F111" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="G111" s="58">
+      <c r="G111" s="54">
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="58"/>
-      <c r="B112" s="58"/>
-      <c r="C112" s="58"/>
-      <c r="D112" s="58"/>
-      <c r="E112" s="58"/>
-      <c r="F112" s="58" t="s">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="54"/>
+      <c r="B112" s="54"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="G112" s="58"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="58"/>
-      <c r="B113" s="58"/>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
-      <c r="E113" s="58"/>
-      <c r="F113" s="58" t="s">
+      <c r="G112" s="54"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="54"/>
+      <c r="B113" s="54"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="G113" s="58"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="58"/>
-      <c r="B114" s="58"/>
-      <c r="C114" s="58"/>
-      <c r="D114" s="58"/>
-      <c r="E114" s="58"/>
-      <c r="F114" s="58"/>
-      <c r="G114" s="58"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="67" t="s">
+      <c r="G113" s="54"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="54"/>
+      <c r="B114" s="54"/>
+      <c r="C114" s="54"/>
+      <c r="D114" s="54"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="54"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="B115" s="67" t="s">
+      <c r="B115" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="C115" s="58"/>
-      <c r="D115" s="63">
+      <c r="C115" s="54"/>
+      <c r="D115" s="58">
         <v>45275</v>
       </c>
-      <c r="E115" s="58" t="s">
+      <c r="E115" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F115" s="58" t="s">
+      <c r="F115" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="G115" s="58">
+      <c r="G115" s="54">
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="58"/>
-      <c r="B116" s="58"/>
-      <c r="C116" s="58"/>
-      <c r="D116" s="58"/>
-      <c r="E116" s="58"/>
-      <c r="F116" s="64" t="s">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="54"/>
+      <c r="B116" s="54"/>
+      <c r="C116" s="54"/>
+      <c r="D116" s="54"/>
+      <c r="E116" s="54"/>
+      <c r="F116" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="G116" s="58"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="58"/>
-      <c r="B117" s="58"/>
-      <c r="C117" s="58"/>
-      <c r="D117" s="58"/>
-      <c r="E117" s="58"/>
-      <c r="F117" s="58" t="s">
+      <c r="G116" s="54"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="54"/>
+      <c r="B117" s="54"/>
+      <c r="C117" s="54"/>
+      <c r="D117" s="54"/>
+      <c r="E117" s="54"/>
+      <c r="F117" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G117" s="58"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="58"/>
-      <c r="B118" s="58"/>
-      <c r="C118" s="58"/>
-      <c r="D118" s="58"/>
-      <c r="E118" s="58"/>
-      <c r="F118" s="64" t="s">
+      <c r="G117" s="54"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="54"/>
+      <c r="B118" s="54"/>
+      <c r="C118" s="54"/>
+      <c r="D118" s="54"/>
+      <c r="E118" s="54"/>
+      <c r="F118" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="G118" s="58"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="58"/>
-      <c r="B119" s="58"/>
-      <c r="C119" s="58"/>
-      <c r="D119" s="58"/>
-      <c r="E119" s="58"/>
-      <c r="F119" s="58" t="s">
+      <c r="G118" s="54"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="54"/>
+      <c r="B119" s="54"/>
+      <c r="C119" s="54"/>
+      <c r="D119" s="54"/>
+      <c r="E119" s="54"/>
+      <c r="F119" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G119" s="58"/>
+      <c r="G119" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -6604,13 +6521,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.15625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>229</v>
       </c>
@@ -6618,10 +6535,10 @@
         <v>230</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="49" t="s">
         <v>231</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>232</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -6655,7 +6572,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>318</v>
       </c>
@@ -6681,419 +6598,419 @@
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>318</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="54" t="s">
         <v>250</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="54">
         <v>2020</v>
       </c>
-      <c r="J4" s="58" t="s">
+      <c r="J4" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="58" t="s">
+      <c r="K4" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="L4" s="58" t="s">
+      <c r="L4" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="M4" s="58" t="s">
+      <c r="M4" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>318</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="54" t="s">
         <v>257</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5" s="54">
         <v>2016</v>
       </c>
-      <c r="J5" s="58" t="s">
+      <c r="J5" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="M5" s="58" t="s">
+      <c r="M5" s="54" t="s">
         <v>260</v>
       </c>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58" t="s">
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>318</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="54">
         <v>2021</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="K6" s="58"/>
-      <c r="L6" s="61" t="s">
+      <c r="K6" s="54"/>
+      <c r="L6" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="M6" s="58" t="s">
+      <c r="M6" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>318</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="54">
         <v>2015</v>
       </c>
-      <c r="J7" s="58" t="s">
+      <c r="J7" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58" t="s">
+      <c r="K7" s="54"/>
+      <c r="L7" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="M7" s="58"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="M7" s="54"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>318</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="54">
         <v>2022</v>
       </c>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58" t="s">
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>318</v>
       </c>
       <c r="C9">
         <v>7</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58" t="s">
+      <c r="G9" s="54"/>
+      <c r="H9" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="54">
         <v>2019</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58" t="s">
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>318</v>
       </c>
       <c r="C10">
         <v>8</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="54" t="s">
         <v>279</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="I10" s="58">
+      <c r="I10" s="54">
         <v>2023</v>
       </c>
-      <c r="J10" s="58" t="s">
+      <c r="J10" s="54" t="s">
         <v>282</v>
       </c>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58" t="s">
+      <c r="K10" s="54"/>
+      <c r="L10" s="54" t="s">
         <v>283</v>
       </c>
-      <c r="M10" s="58" t="s">
+      <c r="M10" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="55"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>318</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="54" t="s">
         <v>285</v>
       </c>
-      <c r="G11" s="58" t="s">
+      <c r="G11" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="54">
         <v>2021</v>
       </c>
-      <c r="J11" s="58" t="s">
+      <c r="J11" s="54" t="s">
         <v>288</v>
       </c>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58" t="s">
+      <c r="K11" s="54"/>
+      <c r="L11" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="M11" s="58" t="s">
+      <c r="M11" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>318</v>
       </c>
       <c r="C12">
         <v>10</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="54" t="s">
         <v>291</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="54" t="s">
         <v>293</v>
       </c>
-      <c r="I12" s="58">
+      <c r="I12" s="54">
         <v>2023</v>
       </c>
-      <c r="J12" s="58" t="s">
+      <c r="J12" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58" t="s">
+      <c r="K12" s="54"/>
+      <c r="L12" s="54" t="s">
         <v>295</v>
       </c>
-      <c r="M12" s="58" t="s">
+      <c r="M12" s="54" t="s">
         <v>296</v>
       </c>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>318</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="54" t="s">
         <v>297</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G13" s="54" t="s">
         <v>298</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="I13" s="58">
+      <c r="I13" s="54">
         <v>2004</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58" t="s">
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54" t="s">
         <v>301</v>
       </c>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>318</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="54" t="s">
         <v>302</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="54" t="s">
         <v>303</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14" s="54">
         <v>2020</v>
       </c>
-      <c r="J14" s="58" t="s">
+      <c r="J14" s="54" t="s">
         <v>282</v>
       </c>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58" t="s">
+      <c r="K14" s="54"/>
+      <c r="L14" s="54" t="s">
         <v>305</v>
       </c>
-      <c r="M14" s="58" t="s">
+      <c r="M14" s="54" t="s">
         <v>306</v>
       </c>
-      <c r="N14" s="60"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="55"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>318</v>
       </c>
       <c r="C15">
         <v>13</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="54" t="s">
         <v>307</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="54" t="s">
         <v>309</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="54">
         <v>2017</v>
       </c>
-      <c r="J15" s="58" t="s">
+      <c r="J15" s="54" t="s">
         <v>310</v>
       </c>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58" t="s">
+      <c r="K15" s="54"/>
+      <c r="L15" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="M15" s="58" t="s">
+      <c r="M15" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N15" s="55"/>
+      <c r="O15" s="55"/>
+      <c r="P15" s="55"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>318</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="54" t="s">
         <v>314</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="I16" s="58">
+      <c r="I16" s="54">
         <v>2023</v>
       </c>
-      <c r="J16" s="58" t="s">
+      <c r="J16" s="54" t="s">
         <v>316</v>
       </c>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58" t="s">
+      <c r="K16" s="54"/>
+      <c r="L16" s="54" t="s">
         <v>317</v>
       </c>
-      <c r="M16" s="58" t="s">
+      <c r="M16" s="54" t="s">
         <v>317</v>
       </c>
     </row>
